--- a/Base_Orcamentos.xlsx
+++ b/Base_Orcamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Orcamento\CONTROLE DE ORÇAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88D02431-F48A-4F76-8173-368D659E082D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A9698F-F80F-455D-8756-5B13C1A1B577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3CB44C3C-8656-4548-BBD3-F080271F0230}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{495ACB26-57DB-4BC2-9659-FD6F45A21599}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Orcamentos" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="412">
   <si>
     <t>Nº Orçamento</t>
   </si>
@@ -98,9 +98,6 @@
     <t>Ticket Médio</t>
   </si>
   <si>
-    <t>Coluna S (Livre/Outros)</t>
-  </si>
-  <si>
     <t>Status do Orçamento</t>
   </si>
   <si>
@@ -176,6 +173,9 @@
     <t>ROT 100mm X 100mm X 1 C | 52 M  c/ 500 ROT</t>
   </si>
   <si>
+    <t>Em Negociação</t>
+  </si>
+  <si>
     <t>Mínima</t>
   </si>
   <si>
@@ -464,6 +464,9 @@
     <t>R.14 TÉRMICO 72G DRY</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
     <t>ORC 26081902</t>
   </si>
   <si>
@@ -617,6 +620,9 @@
     <t>ROT 75mm X 50mm X 1 C | 45 M  c/ 840 ETIQ</t>
   </si>
   <si>
+    <t>Perdido</t>
+  </si>
+  <si>
     <t>Condição de Pagamento</t>
   </si>
   <si>
@@ -824,6 +830,9 @@
     <t>ETIQ 90mm X 55mm X 1 C | 45,5 M  c/ 780 ETIQ</t>
   </si>
   <si>
+    <t>Cancelado</t>
+  </si>
+  <si>
     <t>ETIQ 90mm X 25mm X  C | 45 M  c/ 1600 ETIQ</t>
   </si>
   <si>
@@ -1145,127 +1154,130 @@
     <t>ETIQ 84mm X 42mm X 1 C | METRAGEM A DEFINIR</t>
   </si>
   <si>
+    <t>ORC 26092503</t>
+  </si>
+  <si>
+    <t>M A FRENA &amp; CIA LTDA – SUPER KIKO</t>
+  </si>
+  <si>
+    <t>WALDENIR</t>
+  </si>
+  <si>
+    <t>ETIQ 70mm X 70mm X 1 C | METRAGEM A DEFINIR</t>
+  </si>
+  <si>
+    <t>ORC 26092803</t>
+  </si>
+  <si>
+    <t>MERCADINHO PALLADINO</t>
+  </si>
+  <si>
+    <t>ETIQ 80mm X 95mm X 1 C | 45 M  c/ 450 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26092902</t>
+  </si>
+  <si>
+    <t>SLIP</t>
+  </si>
+  <si>
+    <t>ETIQ 90mm X 110mm X 1 C | 90 M  c/ 790 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26093001</t>
+  </si>
+  <si>
+    <t>CASAGRANDE SUPERMERCADOS LTDA</t>
+  </si>
+  <si>
+    <t>ROT 55mm X 90mm X 1 C | 93 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ROT 130mm X 130mm X 1 C | 133 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ROT 80mm X 80mm X 1 C | 83 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ORC 26093002</t>
+  </si>
+  <si>
+    <t>EXTRAFRUTI S/A – COMERCIO DE HORTIFRUTIGRANJEIROS</t>
+  </si>
+  <si>
+    <t>ALOIZIO</t>
+  </si>
+  <si>
+    <t>ETIQ 80mm X 80mm X 1 C | 83 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ROT 65mm X 100mm X 1 C | 103 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 40mm X 40mm X 2 C | 21,5 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 40mm X 57mm X 2 C | 30 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 50mm X 120mm X 2 C | 123 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26093003</t>
+  </si>
+  <si>
+    <t>ETIQ 21mm X 21mm X 4 C | 60 M  c/ 10000 ETIQ</t>
+  </si>
+  <si>
+    <t>ROT 58mm X 83mm X 1 C | 86 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 30mm X 50mm X 3 C | 53 M  c/ 3000 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 100mm X 120mm X 2 C | 60 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>G.16  PAPEL MONOLÚCIDO</t>
+  </si>
+  <si>
+    <t>ORC 26093004</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO NOVO</t>
+  </si>
+  <si>
+    <t>ETIQ 50mm X 100mm X 1 C | 103 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ROT 90mm X 90mm X 1 C | 93 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 40mm X 40mm X 1 C | 43 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26093005</t>
+  </si>
+  <si>
+    <t>FV – DIST. DE CARNES E PESCADOS LTDA</t>
+  </si>
+  <si>
+    <t>ROT 100mm X 150mm X 1 C | 153 M  c/ 1000 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 110mm X 130mm X 1 C | 130 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 90mm X 130mm X 1 C | 133 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ETIQ 108mm X 150mm X 1 C | 153 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100101</t>
+  </si>
+  <si>
     <t>ETIQ 85mm X 32mm X 1 C | 175 M  c/ 5000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26092503</t>
-  </si>
-  <si>
-    <t>M A FRENA &amp; CIA LTDA – SUPER KIKO</t>
-  </si>
-  <si>
-    <t>WALDENIR</t>
-  </si>
-  <si>
-    <t>ETIQ 70mm X 70mm X 1 C | METRAGEM A DEFINIR</t>
-  </si>
-  <si>
-    <t>ORC 26092803</t>
-  </si>
-  <si>
-    <t>MERCADINHO PALLADINO</t>
-  </si>
-  <si>
-    <t>ETIQ 80mm X 95mm X 1 C | 45 M  c/ 450 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26092902</t>
-  </si>
-  <si>
-    <t>SLIP</t>
-  </si>
-  <si>
-    <t>ETIQ 90mm X 110mm X 1 C | 90 M  c/ 790 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26093001</t>
-  </si>
-  <si>
-    <t>CASAGRANDE SUPERMERCADOS LTDA</t>
-  </si>
-  <si>
-    <t>ROT 55mm X 90mm X 1 C | 93 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ROT 130mm X 130mm X 1 C | 133 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ROT 80mm X 80mm X 1 C | 83 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ORC 26093002</t>
-  </si>
-  <si>
-    <t>EXTRAFRUTI S/A – COMERCIO DE HORTIFRUTIGRANJEIROS</t>
-  </si>
-  <si>
-    <t>ALOIZIO</t>
-  </si>
-  <si>
-    <t>ETIQ 80mm X 80mm X 1 C | 83 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ROT 65mm X 100mm X 1 C | 103 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ETIQ 40mm X 40mm X 2 C | 21,5 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 40mm X 57mm X 2 C | 30 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 50mm X 120mm X 2 C | 123 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26093003</t>
-  </si>
-  <si>
-    <t>ETIQ 21mm X 21mm X 4 C | 60 M  c/ 10000 ETIQ</t>
-  </si>
-  <si>
-    <t>ROT 58mm X 83mm X 1 C | 86 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ETIQ 30mm X 50mm X 3 C | 53 M  c/ 3000 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 100mm X 120mm X 2 C | 60 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>G.16  PAPEL MONOLÚCIDO</t>
-  </si>
-  <si>
-    <t>ORC 26093004</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO NOVO</t>
-  </si>
-  <si>
-    <t>ETIQ 50mm X 100mm X 1 C | 103 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ROT 90mm X 90mm X 1 C | 93 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ETIQ 40mm X 40mm X 1 C | 43 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26093005</t>
-  </si>
-  <si>
-    <t>FV – DIST. DE CARNES E PESCADOS LTDA</t>
-  </si>
-  <si>
-    <t>ROT 100mm X 150mm X 1 C | 153 M  c/ 1000 ROT</t>
-  </si>
-  <si>
-    <t>ETIQ 110mm X 130mm X 1 C | 130 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 90mm X 130mm X 1 C | 133 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ETIQ 108mm X 150mm X 1 C | 153 M  c/ 1000 ETIQ</t>
   </si>
 </sst>
 </file>
@@ -1273,8 +1285,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="7" formatCode="&quot;R$&quot;#,##0.00_);\(&quot;R$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;#,##0.00_);\(&quot;R$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1352,26 +1364,26 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1678,9 +1690,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4BD2558-146D-4E99-A70F-AC22A85E688E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07452749-6F0B-425E-BFD1-336AFE831639}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:Y390"/>
+  <dimension ref="A1:X390"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1708,15 +1720,15 @@
     <col min="23" max="23" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q1" s="8">
         <v>170894.7</v>
       </c>
       <c r="R1" s="8">
-        <v>1315319.04</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>1364979.52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1789,31 +1801,28 @@
       <c r="X2" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" t="s">
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>25</v>
       </c>
       <c r="B3" s="7">
         <v>46254.386481481481</v>
       </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
       </c>
       <c r="H3" s="1">
         <v>160</v>
@@ -1832,27 +1841,27 @@
       </c>
       <c r="V3" s="7"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="7">
         <v>46239.435243055559</v>
       </c>
       <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
       </c>
       <c r="H4" s="1">
         <v>20</v>
@@ -1889,27 +1898,27 @@
       </c>
       <c r="V4" s="7"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="7">
         <v>46239.435243055559</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H5" s="1">
         <v>85</v>
@@ -1946,27 +1955,27 @@
       </c>
       <c r="V5" s="7"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="7">
         <v>46239.43577546296</v>
       </c>
       <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
       </c>
       <c r="H6" s="1">
         <v>40</v>
@@ -2003,27 +2012,27 @@
       </c>
       <c r="V6" s="7"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="7">
         <v>46239.626168981478</v>
       </c>
       <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>42</v>
       </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H7" s="1">
         <v>65</v>
@@ -2058,12 +2067,15 @@
       <c r="R7" s="8">
         <v>3253.58</v>
       </c>
+      <c r="S7" t="s">
+        <v>43</v>
+      </c>
       <c r="T7" t="s">
         <v>44</v>
       </c>
       <c r="V7" s="7"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -2074,7 +2086,7 @@
         <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
         <v>47</v>
@@ -2120,7 +2132,7 @@
       </c>
       <c r="V8" s="7"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -2131,7 +2143,7 @@
         <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
         <v>52</v>
@@ -2140,7 +2152,7 @@
         <v>53</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9" s="1">
         <v>100</v>
@@ -2177,7 +2189,7 @@
       </c>
       <c r="V9" s="7"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -2197,7 +2209,7 @@
         <v>58</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10" s="1">
         <v>80</v>
@@ -2234,7 +2246,7 @@
       </c>
       <c r="V10" s="7"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -2245,7 +2257,7 @@
         <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
         <v>61</v>
@@ -2271,12 +2283,15 @@
       <c r="R11" s="8">
         <v>28183.91</v>
       </c>
+      <c r="S11" t="s">
+        <v>43</v>
+      </c>
       <c r="T11" t="s">
         <v>44</v>
       </c>
       <c r="V11" s="7"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -2287,7 +2302,7 @@
         <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -2313,12 +2328,15 @@
       <c r="R12" s="8">
         <v>28183.91</v>
       </c>
+      <c r="S12" t="s">
+        <v>43</v>
+      </c>
       <c r="T12" t="s">
         <v>44</v>
       </c>
       <c r="V12" s="7"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -2357,7 +2375,7 @@
       </c>
       <c r="V13" s="7"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -2368,7 +2386,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
         <v>72</v>
@@ -2377,7 +2395,7 @@
         <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H14" s="1">
         <v>145</v>
@@ -2414,7 +2432,7 @@
       </c>
       <c r="V14" s="7"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -2425,10 +2443,10 @@
         <v>75</v>
       </c>
       <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
         <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
       </c>
       <c r="F15" t="s">
         <v>76</v>
@@ -2471,7 +2489,7 @@
       </c>
       <c r="V15" s="7"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -2482,16 +2500,16 @@
         <v>79</v>
       </c>
       <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
         <v>27</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
       </c>
       <c r="F16" t="s">
         <v>80</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="1">
         <v>30</v>
@@ -2539,16 +2557,16 @@
         <v>79</v>
       </c>
       <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
         <v>27</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
       </c>
       <c r="F17" t="s">
         <v>81</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H17" s="1">
         <v>30</v>
@@ -2596,16 +2614,16 @@
         <v>79</v>
       </c>
       <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
         <v>27</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
       </c>
       <c r="F18" t="s">
         <v>82</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H18" s="1">
         <v>30</v>
@@ -2653,10 +2671,10 @@
         <v>79</v>
       </c>
       <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
         <v>27</v>
-      </c>
-      <c r="E19" t="s">
-        <v>28</v>
       </c>
       <c r="F19" t="s">
         <v>83</v>
@@ -2710,16 +2728,16 @@
         <v>79</v>
       </c>
       <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
         <v>27</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
       </c>
       <c r="F20" t="s">
         <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H20" s="1">
         <v>100</v>
@@ -2767,7 +2785,7 @@
         <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
         <v>47</v>
@@ -2776,7 +2794,7 @@
         <v>87</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H21" s="1">
         <v>70</v>
@@ -2824,7 +2842,7 @@
         <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
         <v>47</v>
@@ -2863,10 +2881,10 @@
         <v>79</v>
       </c>
       <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
         <v>27</v>
-      </c>
-      <c r="E23" t="s">
-        <v>28</v>
       </c>
       <c r="F23" t="s">
         <v>93</v>
@@ -2920,10 +2938,10 @@
         <v>96</v>
       </c>
       <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
         <v>27</v>
-      </c>
-      <c r="E24" t="s">
-        <v>28</v>
       </c>
       <c r="F24" t="s">
         <v>97</v>
@@ -2977,10 +2995,10 @@
         <v>96</v>
       </c>
       <c r="D25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s">
         <v>27</v>
-      </c>
-      <c r="E25" t="s">
-        <v>28</v>
       </c>
       <c r="F25" t="s">
         <v>99</v>
@@ -3034,10 +3052,10 @@
         <v>101</v>
       </c>
       <c r="D26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
         <v>27</v>
-      </c>
-      <c r="E26" t="s">
-        <v>28</v>
       </c>
       <c r="F26" t="s">
         <v>102</v>
@@ -3091,10 +3109,10 @@
         <v>104</v>
       </c>
       <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
         <v>27</v>
-      </c>
-      <c r="E27" t="s">
-        <v>28</v>
       </c>
       <c r="F27" t="s">
         <v>105</v>
@@ -3148,10 +3166,10 @@
         <v>104</v>
       </c>
       <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
         <v>27</v>
-      </c>
-      <c r="E28" t="s">
-        <v>28</v>
       </c>
       <c r="F28" t="s">
         <v>106</v>
@@ -3205,10 +3223,10 @@
         <v>104</v>
       </c>
       <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
         <v>27</v>
-      </c>
-      <c r="E29" t="s">
-        <v>28</v>
       </c>
       <c r="F29" t="s">
         <v>107</v>
@@ -3262,10 +3280,10 @@
         <v>109</v>
       </c>
       <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
         <v>27</v>
-      </c>
-      <c r="E30" t="s">
-        <v>28</v>
       </c>
       <c r="F30" t="s">
         <v>110</v>
@@ -3319,16 +3337,16 @@
         <v>109</v>
       </c>
       <c r="D31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" t="s">
         <v>27</v>
-      </c>
-      <c r="E31" t="s">
-        <v>28</v>
       </c>
       <c r="F31" t="s">
         <v>112</v>
       </c>
       <c r="G31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H31" s="1">
         <v>150</v>
@@ -3376,16 +3394,16 @@
         <v>109</v>
       </c>
       <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
         <v>27</v>
-      </c>
-      <c r="E32" t="s">
-        <v>28</v>
       </c>
       <c r="F32" t="s">
         <v>112</v>
       </c>
       <c r="G32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H32" s="1">
         <v>150</v>
@@ -3433,10 +3451,10 @@
         <v>109</v>
       </c>
       <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
         <v>27</v>
-      </c>
-      <c r="E33" t="s">
-        <v>28</v>
       </c>
       <c r="F33" t="s">
         <v>113</v>
@@ -3490,7 +3508,7 @@
         <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E34" t="s">
         <v>116</v>
@@ -3499,7 +3517,7 @@
         <v>117</v>
       </c>
       <c r="G34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H34" s="1">
         <v>500</v>
@@ -3515,6 +3533,9 @@
       </c>
       <c r="R34" s="8">
         <v>24624.51</v>
+      </c>
+      <c r="S34" t="s">
+        <v>43</v>
       </c>
       <c r="T34" t="s">
         <v>44</v>
@@ -3532,7 +3553,7 @@
         <v>115</v>
       </c>
       <c r="D35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E35" t="s">
         <v>116</v>
@@ -3541,7 +3562,7 @@
         <v>118</v>
       </c>
       <c r="G35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H35" s="1">
         <v>150</v>
@@ -3557,6 +3578,9 @@
       </c>
       <c r="R35" s="8">
         <v>11485.6</v>
+      </c>
+      <c r="S35" t="s">
+        <v>43</v>
       </c>
       <c r="T35" t="s">
         <v>44</v>
@@ -3583,7 +3607,7 @@
         <v>123</v>
       </c>
       <c r="G36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H36" s="1">
         <v>60</v>
@@ -3613,7 +3637,7 @@
         <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
@@ -3670,7 +3694,7 @@
         <v>129</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E38" t="s">
         <v>47</v>
@@ -3804,6 +3828,9 @@
       <c r="R40" s="8">
         <v>4077.8</v>
       </c>
+      <c r="S40" t="s">
+        <v>140</v>
+      </c>
       <c r="T40" t="s">
         <v>44</v>
       </c>
@@ -3811,22 +3838,22 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B41" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" t="s">
         <v>27</v>
       </c>
-      <c r="E41" t="s">
-        <v>28</v>
-      </c>
       <c r="F41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G41" t="s">
         <v>49</v>
@@ -3868,22 +3895,22 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B42" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" t="s">
         <v>27</v>
       </c>
-      <c r="E42" t="s">
-        <v>28</v>
-      </c>
       <c r="F42" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G42" t="s">
         <v>49</v>
@@ -3925,22 +3952,22 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B43" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" t="s">
         <v>27</v>
       </c>
-      <c r="E43" t="s">
-        <v>28</v>
-      </c>
       <c r="F43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G43" t="s">
         <v>49</v>
@@ -3982,22 +4009,22 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B44" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D44" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" t="s">
         <v>27</v>
       </c>
-      <c r="E44" t="s">
-        <v>28</v>
-      </c>
       <c r="F44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G44" t="s">
         <v>49</v>
@@ -4039,22 +4066,22 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B45" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D45" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" t="s">
         <v>27</v>
       </c>
-      <c r="E45" t="s">
-        <v>28</v>
-      </c>
       <c r="F45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G45" t="s">
         <v>49</v>
@@ -4096,22 +4123,22 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B46" s="7">
         <v>46253.684652777774</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" t="s">
         <v>27</v>
       </c>
-      <c r="E46" t="s">
-        <v>28</v>
-      </c>
       <c r="F46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G46" t="s">
         <v>63</v>
@@ -4153,22 +4180,22 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B47" s="7">
         <v>46253.684652777774</v>
       </c>
       <c r="C47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D47" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" t="s">
         <v>27</v>
       </c>
-      <c r="E47" t="s">
-        <v>28</v>
-      </c>
       <c r="F47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G47" t="s">
         <v>63</v>
@@ -4210,25 +4237,25 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B48" s="7">
         <v>46253.707175925927</v>
       </c>
       <c r="C48" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H48" s="1">
         <v>110</v>
@@ -4263,6 +4290,9 @@
       <c r="R48" s="8">
         <v>4320.16</v>
       </c>
+      <c r="S48" t="s">
+        <v>43</v>
+      </c>
       <c r="T48" t="s">
         <v>44</v>
       </c>
@@ -4270,22 +4300,22 @@
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B49" s="7">
         <v>46254.331678240742</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G49" t="s">
         <v>111</v>
@@ -4323,6 +4353,9 @@
       <c r="R49" s="8">
         <v>4133.8900000000003</v>
       </c>
+      <c r="S49" t="s">
+        <v>43</v>
+      </c>
       <c r="T49" t="s">
         <v>44</v>
       </c>
@@ -4330,25 +4363,25 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B50" s="7">
         <v>46255.398784722223</v>
       </c>
       <c r="C50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D50" t="s">
         <v>121</v>
       </c>
       <c r="E50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H50" s="1">
         <v>50</v>
@@ -4387,22 +4420,22 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B51" s="7">
         <v>46255.395833333336</v>
       </c>
       <c r="C51" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E51" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G51" t="s">
         <v>69</v>
@@ -4444,22 +4477,22 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B52" s="7">
         <v>46255.395833333336</v>
       </c>
       <c r="C52" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F52" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G52" t="s">
         <v>69</v>
@@ -4501,22 +4534,22 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B53" s="7">
         <v>46255.614803240744</v>
       </c>
       <c r="C53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G53" t="s">
         <v>91</v>
@@ -4554,6 +4587,9 @@
       <c r="R53" s="8">
         <v>3985.14</v>
       </c>
+      <c r="S53" t="s">
+        <v>43</v>
+      </c>
       <c r="T53" t="s">
         <v>44</v>
       </c>
@@ -4561,25 +4597,25 @@
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B54" s="7">
         <v>46255.715358796297</v>
       </c>
       <c r="C54" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H54" s="1">
         <v>50</v>
@@ -4618,25 +4654,25 @@
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B55" s="7">
         <v>46255.715358796297</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F55" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H55" s="1">
         <v>125</v>
@@ -4675,25 +4711,25 @@
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B56" s="7">
         <v>46255.705381944441</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F56" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H56" s="1">
         <v>1595</v>
@@ -4732,25 +4768,25 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B57" s="7">
         <v>46255.705381944441</v>
       </c>
       <c r="C57" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F57" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H57" s="1">
         <v>130</v>
@@ -4789,25 +4825,25 @@
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B58" s="7">
         <v>46280.584108796298</v>
       </c>
       <c r="C58" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E58" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F58" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H58" s="1">
         <v>80</v>
@@ -4846,25 +4882,25 @@
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B59" s="7">
         <v>46258.660266203704</v>
       </c>
       <c r="C59" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E59" t="s">
         <v>61</v>
       </c>
       <c r="F59" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H59" s="1">
         <v>70</v>
@@ -4895,32 +4931,35 @@
       <c r="R59" s="8">
         <v>2753.87</v>
       </c>
+      <c r="S59" t="s">
+        <v>43</v>
+      </c>
       <c r="T59" t="s">
         <v>44</v>
       </c>
       <c r="V59" s="7"/>
       <c r="W59" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B60" s="7">
         <v>46258.660601851851</v>
       </c>
       <c r="C60" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E60" t="s">
         <v>61</v>
       </c>
       <c r="F60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G60" t="s">
         <v>91</v>
@@ -4944,35 +4983,38 @@
       <c r="R60" s="8">
         <v>3602.61</v>
       </c>
+      <c r="S60" t="s">
+        <v>192</v>
+      </c>
       <c r="T60" t="s">
         <v>44</v>
       </c>
       <c r="U60" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="V60" s="7"/>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B61" s="7">
         <v>46258.69740740741</v>
       </c>
       <c r="C61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F61" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H61" s="1">
         <v>30</v>
@@ -5005,25 +5047,25 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B62" s="7">
         <v>46258.69740740741</v>
       </c>
       <c r="C62" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F62" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G62" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H62" s="1">
         <v>10</v>
@@ -5048,22 +5090,22 @@
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B63" s="7">
         <v>46259.568854166668</v>
       </c>
       <c r="C63" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F63" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G63" t="s">
         <v>63</v>
@@ -5087,22 +5129,22 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B64" s="7">
         <v>46259.617465277777</v>
       </c>
       <c r="C64" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" t="s">
         <v>27</v>
       </c>
-      <c r="E64" t="s">
-        <v>28</v>
-      </c>
       <c r="F64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G64" t="s">
         <v>98</v>
@@ -5144,22 +5186,22 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B65" s="7">
         <v>46259.72284722222</v>
       </c>
       <c r="C65" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F65" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G65" t="s">
         <v>98</v>
@@ -5197,6 +5239,9 @@
       <c r="R65" s="8">
         <v>5405.67</v>
       </c>
+      <c r="S65" t="s">
+        <v>43</v>
+      </c>
       <c r="T65" t="s">
         <v>44</v>
       </c>
@@ -5204,22 +5249,22 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B66" s="7">
         <v>46259.72284722222</v>
       </c>
       <c r="C66" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F66" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G66" t="s">
         <v>111</v>
@@ -5257,6 +5302,9 @@
       <c r="R66" s="8">
         <v>5405.67</v>
       </c>
+      <c r="S66" t="s">
+        <v>43</v>
+      </c>
       <c r="T66" t="s">
         <v>44</v>
       </c>
@@ -5264,13 +5312,13 @@
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B67" s="7">
         <v>46259.724189814813</v>
       </c>
       <c r="C67" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D67" t="s">
         <v>121</v>
@@ -5279,10 +5327,10 @@
         <v>137</v>
       </c>
       <c r="F67" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H67" s="1">
         <v>435</v>
@@ -5317,6 +5365,9 @@
       <c r="R67" s="8">
         <v>3185.45</v>
       </c>
+      <c r="S67" t="s">
+        <v>140</v>
+      </c>
       <c r="T67" t="s">
         <v>44</v>
       </c>
@@ -5324,22 +5375,22 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B68" s="7">
         <v>46260.699502314812</v>
       </c>
       <c r="C68" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E68" t="s">
         <v>116</v>
       </c>
       <c r="F68" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G68" t="s">
         <v>49</v>
@@ -5363,35 +5414,38 @@
       <c r="R68" s="8">
         <v>2558.5</v>
       </c>
+      <c r="S68" t="s">
+        <v>192</v>
+      </c>
       <c r="T68" t="s">
         <v>44</v>
       </c>
       <c r="U68" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V68" s="7"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B69" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C69" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
         <v>47</v>
       </c>
       <c r="F69" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H69" s="1">
         <v>100</v>
@@ -5424,22 +5478,22 @@
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B70" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C70" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
         <v>47</v>
       </c>
       <c r="F70" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G70" t="s">
         <v>94</v>
@@ -5478,22 +5532,22 @@
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B71" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C71" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E71" t="s">
         <v>47</v>
       </c>
       <c r="F71" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G71" t="s">
         <v>94</v>
@@ -5532,25 +5586,25 @@
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B72" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C72" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E72" t="s">
         <v>47</v>
       </c>
       <c r="F72" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H72" s="1">
         <v>80</v>
@@ -5586,25 +5640,25 @@
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B73" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C73" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E73" t="s">
         <v>47</v>
       </c>
       <c r="F73" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G73" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H73" s="1">
         <v>130</v>
@@ -5637,25 +5691,25 @@
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B74" s="7">
         <v>46260.707881944443</v>
       </c>
       <c r="C74" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E74" t="s">
         <v>47</v>
       </c>
       <c r="F74" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H74" s="1">
         <v>80</v>
@@ -5691,25 +5745,25 @@
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B75" s="7">
         <v>46260.707881944443</v>
       </c>
       <c r="C75" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E75" t="s">
         <v>47</v>
       </c>
       <c r="F75" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G75" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H75" s="1">
         <v>120</v>
@@ -5742,25 +5796,25 @@
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B76" s="7">
         <v>46260.707881944443</v>
       </c>
       <c r="C76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D76" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E76" t="s">
         <v>47</v>
       </c>
       <c r="F76" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H76" s="1">
         <v>20</v>
@@ -5793,25 +5847,25 @@
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B77" s="7">
         <v>46260.707881944443</v>
       </c>
       <c r="C77" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E77" t="s">
         <v>47</v>
       </c>
       <c r="F77" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H77" s="1">
         <v>163</v>
@@ -5844,25 +5898,25 @@
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B78" s="7">
         <v>46260.70826388889</v>
       </c>
       <c r="C78" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D78" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E78" t="s">
         <v>47</v>
       </c>
       <c r="F78" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G78" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H78" s="1">
         <v>36</v>
@@ -5895,25 +5949,25 @@
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B79" s="7">
         <v>46260.70826388889</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E79" t="s">
         <v>47</v>
       </c>
       <c r="F79" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H79" s="1">
         <v>45</v>
@@ -5946,25 +6000,25 @@
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B80" s="7">
         <v>46260.70826388889</v>
       </c>
       <c r="C80" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D80" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E80" t="s">
         <v>47</v>
       </c>
       <c r="F80" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H80" s="1">
         <v>35</v>
@@ -5997,22 +6051,22 @@
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B81" s="7">
         <v>46281.721875000003</v>
       </c>
       <c r="C81" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D81" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E81" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F81" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G81" t="s">
         <v>49</v>
@@ -6050,6 +6104,9 @@
       <c r="R81" s="8">
         <v>7422.4</v>
       </c>
+      <c r="S81" t="s">
+        <v>43</v>
+      </c>
       <c r="T81" t="s">
         <v>44</v>
       </c>
@@ -6057,22 +6114,22 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B82" s="7">
         <v>46281.721875000003</v>
       </c>
       <c r="C82" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F82" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G82" t="s">
         <v>49</v>
@@ -6110,6 +6167,9 @@
       <c r="R82" s="8">
         <v>7422.4</v>
       </c>
+      <c r="S82" t="s">
+        <v>43</v>
+      </c>
       <c r="T82" t="s">
         <v>44</v>
       </c>
@@ -6117,25 +6177,25 @@
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B83" s="7">
         <v>46261.662106481483</v>
       </c>
       <c r="C83" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D83" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" t="s">
         <v>27</v>
       </c>
-      <c r="E83" t="s">
-        <v>28</v>
-      </c>
       <c r="F83" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G83" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H83" s="1">
         <v>10</v>
@@ -6174,25 +6234,25 @@
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B84" s="7">
         <v>46261.662106481483</v>
       </c>
       <c r="C84" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D84" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" t="s">
         <v>27</v>
       </c>
-      <c r="E84" t="s">
-        <v>28</v>
-      </c>
       <c r="F84" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G84" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H84" s="1">
         <v>10</v>
@@ -6231,25 +6291,25 @@
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B85" s="7">
         <v>46280.713750000003</v>
       </c>
       <c r="C85" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D85" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E85" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F85" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G85" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H85" s="1">
         <v>1000</v>
@@ -6274,25 +6334,25 @@
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B86" s="7">
         <v>46266.589988425927</v>
       </c>
       <c r="C86" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D86" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E86" t="s">
         <v>116</v>
       </c>
       <c r="F86" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H86" s="1">
         <v>32</v>
@@ -6313,6 +6373,9 @@
       <c r="R86" s="8">
         <v>3803.52</v>
       </c>
+      <c r="S86" t="s">
+        <v>140</v>
+      </c>
       <c r="T86" t="s">
         <v>44</v>
       </c>
@@ -6320,25 +6383,25 @@
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B87" s="7">
         <v>46266.556886574072</v>
       </c>
       <c r="C87" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D87" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E87" t="s">
         <v>116</v>
       </c>
       <c r="F87" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G87" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H87" s="1">
         <v>150</v>
@@ -6355,6 +6418,9 @@
       <c r="R87" s="8">
         <v>9946.5</v>
       </c>
+      <c r="S87" t="s">
+        <v>43</v>
+      </c>
       <c r="T87" t="s">
         <v>44</v>
       </c>
@@ -6362,25 +6428,25 @@
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B88" s="7">
         <v>46266.556886574072</v>
       </c>
       <c r="C88" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D88" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E88" t="s">
         <v>116</v>
       </c>
       <c r="F88" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G88" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H88" s="1">
         <v>60</v>
@@ -6397,6 +6463,9 @@
       <c r="R88" s="8">
         <v>10509</v>
       </c>
+      <c r="S88" t="s">
+        <v>43</v>
+      </c>
       <c r="T88" t="s">
         <v>44</v>
       </c>
@@ -6404,22 +6473,22 @@
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B89" s="7">
         <v>46262.725381944445</v>
       </c>
       <c r="C89" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D89" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E89" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F89" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G89" t="s">
         <v>139</v>
@@ -6461,25 +6530,25 @@
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B90" s="7">
         <v>46265.689513888887</v>
       </c>
       <c r="C90" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D90" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E90" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F90" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H90" s="1">
         <v>416</v>
@@ -6508,35 +6577,38 @@
       <c r="R90" s="8">
         <v>9597.1200000000008</v>
       </c>
+      <c r="S90" t="s">
+        <v>262</v>
+      </c>
       <c r="T90" t="s">
         <v>44</v>
       </c>
       <c r="U90" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V90" s="7"/>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B91" s="7">
         <v>46265.689513888887</v>
       </c>
       <c r="C91" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D91" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E91" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F91" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H91" s="1">
         <v>115</v>
@@ -6571,23 +6643,26 @@
       <c r="R91" s="8">
         <v>3381.33</v>
       </c>
+      <c r="S91" t="s">
+        <v>262</v>
+      </c>
       <c r="T91" t="s">
         <v>44</v>
       </c>
       <c r="U91" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="V91" s="7"/>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B92" s="7">
         <v>46279.438460648147</v>
       </c>
       <c r="C92" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D92" t="s">
         <v>121</v>
@@ -6596,10 +6671,10 @@
         <v>116</v>
       </c>
       <c r="F92" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G92" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H92" s="1">
         <v>25</v>
@@ -6634,6 +6709,9 @@
       <c r="R92" s="8">
         <v>3548.63</v>
       </c>
+      <c r="S92" t="s">
+        <v>43</v>
+      </c>
       <c r="T92" t="s">
         <v>44</v>
       </c>
@@ -6641,22 +6719,22 @@
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B93" s="7">
         <v>46267.733101851853</v>
       </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D93" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E93" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F93" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G93" t="s">
         <v>98</v>
@@ -6698,22 +6776,22 @@
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B94" s="7">
         <v>46267.733101851853</v>
       </c>
       <c r="C94" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D94" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E94" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F94" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G94" t="s">
         <v>98</v>
@@ -6755,25 +6833,25 @@
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B95" s="7">
         <v>46268.44902777778</v>
       </c>
       <c r="C95" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D95" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E95" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F95" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G95" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H95" s="1">
         <v>4</v>
@@ -6805,25 +6883,25 @@
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B96" s="7">
         <v>46268.44902777778</v>
       </c>
       <c r="C96" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D96" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F96" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G96" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H96" s="1">
         <v>4</v>
@@ -6855,25 +6933,25 @@
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B97" s="7">
         <v>46268.44902777778</v>
       </c>
       <c r="C97" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D97" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E97" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F97" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G97" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H97" s="1">
         <v>4</v>
@@ -6903,22 +6981,22 @@
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B98" s="7">
         <v>46280.572372685187</v>
       </c>
       <c r="C98" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D98" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E98" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F98" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G98" t="s">
         <v>91</v>
@@ -6956,6 +7034,9 @@
       <c r="R98" s="8">
         <v>4237.3</v>
       </c>
+      <c r="S98" t="s">
+        <v>140</v>
+      </c>
       <c r="T98" t="s">
         <v>44</v>
       </c>
@@ -6963,13 +7044,13 @@
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B99" s="7">
         <v>46273.645821759259</v>
       </c>
       <c r="C99" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D99" t="s">
         <v>66</v>
@@ -6978,10 +7059,10 @@
         <v>61</v>
       </c>
       <c r="F99" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H99" s="1">
         <v>100</v>
@@ -7016,6 +7097,9 @@
       <c r="R99" s="8">
         <v>1483</v>
       </c>
+      <c r="S99" t="s">
+        <v>140</v>
+      </c>
       <c r="T99" t="s">
         <v>44</v>
       </c>
@@ -7023,13 +7107,13 @@
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B100" s="7">
         <v>46273.645821759259</v>
       </c>
       <c r="C100" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D100" t="s">
         <v>66</v>
@@ -7038,10 +7122,10 @@
         <v>61</v>
       </c>
       <c r="F100" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H100" s="1">
         <v>100</v>
@@ -7076,6 +7160,9 @@
       <c r="R100" s="8">
         <v>2542</v>
       </c>
+      <c r="S100" t="s">
+        <v>140</v>
+      </c>
       <c r="T100" t="s">
         <v>44</v>
       </c>
@@ -7083,22 +7170,22 @@
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B101" s="7">
         <v>46280.583483796298</v>
       </c>
       <c r="C101" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D101" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E101" t="s">
         <v>47</v>
       </c>
       <c r="F101" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G101" t="s">
         <v>98</v>
@@ -7140,25 +7227,25 @@
     </row>
     <row r="102" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B102" s="7">
         <v>46275.466377314813</v>
       </c>
       <c r="C102" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D102" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E102" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F102" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H102" s="1">
         <v>60</v>
@@ -7197,25 +7284,25 @@
     </row>
     <row r="103" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B103" s="7">
         <v>46279.439363425925</v>
       </c>
       <c r="C103" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D103" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E103" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F103" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H103" s="1">
         <v>130</v>
@@ -7254,22 +7341,22 @@
     </row>
     <row r="104" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B104" s="7">
         <v>46276.397337962961</v>
       </c>
       <c r="C104" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D104" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E104" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F104" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G104" t="s">
         <v>94</v>
@@ -7311,25 +7398,25 @@
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B105" s="7">
         <v>46279.607939814814</v>
       </c>
       <c r="C105" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D105" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E105" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F105" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H105" s="1">
         <v>160</v>
@@ -7368,22 +7455,22 @@
     </row>
     <row r="106" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B106" s="7">
         <v>46279.619386574072</v>
       </c>
       <c r="C106" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D106" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E106" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F106" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G106" t="s">
         <v>69</v>
@@ -7425,22 +7512,22 @@
     </row>
     <row r="107" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B107" s="7">
         <v>46287.559652777774</v>
       </c>
       <c r="C107" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D107" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E107" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F107" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G107" t="s">
         <v>49</v>
@@ -7482,22 +7569,22 @@
     </row>
     <row r="108" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B108" s="7">
         <v>46287.559652777774</v>
       </c>
       <c r="C108" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D108" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E108" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F108" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G108" t="s">
         <v>49</v>
@@ -7539,25 +7626,25 @@
     </row>
     <row r="109" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B109" s="7">
         <v>46287.559652777774</v>
       </c>
       <c r="C109" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D109" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F109" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H109" s="1">
         <v>195</v>
@@ -7596,25 +7683,25 @@
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B110" s="7">
         <v>46287.559652777774</v>
       </c>
       <c r="C110" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D110" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E110" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F110" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H110" s="1">
         <v>800</v>
@@ -7653,22 +7740,22 @@
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B111" s="7">
         <v>46281.721805555557</v>
       </c>
       <c r="C111" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D111" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E111" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F111" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G111" t="s">
         <v>49</v>
@@ -7710,22 +7797,22 @@
     </row>
     <row r="112" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B112" s="7">
         <v>46281.721805555557</v>
       </c>
       <c r="C112" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D112" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E112" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F112" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G112" t="s">
         <v>49</v>
@@ -7767,25 +7854,25 @@
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B113" s="7">
         <v>46281.721805555557</v>
       </c>
       <c r="C113" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D113" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E113" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F113" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G113" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H113" s="1">
         <v>195</v>
@@ -7824,22 +7911,22 @@
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B114" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C114" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D114" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E114" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F114" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G114" t="s">
         <v>111</v>
@@ -7881,22 +7968,22 @@
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B115" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C115" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D115" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F115" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G115" t="s">
         <v>111</v>
@@ -7938,22 +8025,22 @@
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B116" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C116" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D116" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F116" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G116" t="s">
         <v>111</v>
@@ -7995,25 +8082,25 @@
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B117" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C117" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D117" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E117" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F117" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H117" s="1">
         <v>35</v>
@@ -8052,22 +8139,22 @@
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B118" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C118" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D118" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E118" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F118" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G118" t="s">
         <v>94</v>
@@ -8109,25 +8196,25 @@
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B119" s="7">
         <v>46279.700057870374</v>
       </c>
       <c r="C119" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D119" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E119" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F119" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G119" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H119" s="1">
         <v>500</v>
@@ -8166,25 +8253,25 @@
     </row>
     <row r="120" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B120" s="7">
         <v>46282.705983796295</v>
       </c>
       <c r="C120" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D120" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E120" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F120" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G120" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H120" s="1">
         <v>32</v>
@@ -8223,25 +8310,25 @@
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B121" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C121" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D121" t="s">
+        <v>26</v>
+      </c>
+      <c r="E121" t="s">
         <v>27</v>
       </c>
-      <c r="E121" t="s">
-        <v>28</v>
-      </c>
       <c r="F121" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G121" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H121" s="1">
         <v>40</v>
@@ -8280,25 +8367,25 @@
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B122" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C122" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D122" t="s">
+        <v>26</v>
+      </c>
+      <c r="E122" t="s">
         <v>27</v>
       </c>
-      <c r="E122" t="s">
-        <v>28</v>
-      </c>
       <c r="F122" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G122" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H122" s="1">
         <v>50</v>
@@ -8337,25 +8424,25 @@
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B123" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C123" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D123" t="s">
+        <v>26</v>
+      </c>
+      <c r="E123" t="s">
         <v>27</v>
       </c>
-      <c r="E123" t="s">
-        <v>28</v>
-      </c>
       <c r="F123" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G123" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H123" s="1">
         <v>75</v>
@@ -8394,25 +8481,25 @@
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B124" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C124" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D124" t="s">
+        <v>26</v>
+      </c>
+      <c r="E124" t="s">
         <v>27</v>
       </c>
-      <c r="E124" t="s">
-        <v>28</v>
-      </c>
       <c r="F124" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H124" s="1">
         <v>45</v>
@@ -8451,25 +8538,25 @@
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B125" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C125" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D125" t="s">
+        <v>26</v>
+      </c>
+      <c r="E125" t="s">
         <v>27</v>
       </c>
-      <c r="E125" t="s">
-        <v>28</v>
-      </c>
       <c r="F125" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H125" s="1">
         <v>45</v>
@@ -8508,22 +8595,22 @@
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B126" s="7">
         <v>46287.540856481479</v>
       </c>
       <c r="C126" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D126" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E126" t="s">
         <v>47</v>
       </c>
       <c r="F126" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G126" t="s">
         <v>139</v>
@@ -8565,22 +8652,22 @@
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B127" s="7">
         <v>46287.540856481479</v>
       </c>
       <c r="C127" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D127" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E127" t="s">
         <v>47</v>
       </c>
       <c r="F127" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G127" t="s">
         <v>139</v>
@@ -8622,25 +8709,25 @@
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B128" s="7">
         <v>46287.66646990741</v>
       </c>
       <c r="C128" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D128" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E128" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F128" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G128" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H128" s="1">
         <v>250</v>
@@ -8679,25 +8766,25 @@
     </row>
     <row r="129" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B129" s="7">
         <v>46287.66646990741</v>
       </c>
       <c r="C129" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D129" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E129" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F129" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G129" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H129" s="1">
         <v>40</v>
@@ -8736,25 +8823,25 @@
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B130" s="7">
         <v>46287.66646990741</v>
       </c>
       <c r="C130" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D130" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E130" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F130" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G130" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H130" s="1">
         <v>5000</v>
@@ -8793,25 +8880,25 @@
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B131" s="7">
         <v>46287.649074074077</v>
       </c>
       <c r="C131" t="s">
+        <v>341</v>
+      </c>
+      <c r="D131" t="s">
+        <v>246</v>
+      </c>
+      <c r="E131" t="s">
         <v>338</v>
       </c>
-      <c r="D131" t="s">
-        <v>244</v>
-      </c>
-      <c r="E131" t="s">
-        <v>335</v>
-      </c>
       <c r="F131" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G131" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H131" s="1">
         <v>140</v>
@@ -8850,22 +8937,22 @@
     </row>
     <row r="132" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B132" s="7">
         <v>46287.644872685189</v>
       </c>
       <c r="C132" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D132" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E132" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F132" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G132" t="s">
         <v>139</v>
@@ -8907,25 +8994,25 @@
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B133" s="7">
         <v>46288.702326388891</v>
       </c>
       <c r="C133" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D133" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E133" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F133" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G133" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H133" s="1">
         <v>1116</v>
@@ -8964,25 +9051,25 @@
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B134" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C134" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D134" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E134" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F134" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G134" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H134" s="1">
         <v>50</v>
@@ -9021,25 +9108,25 @@
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B135" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C135" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D135" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E135" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F135" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G135" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H135" s="1">
         <v>80</v>
@@ -9078,25 +9165,25 @@
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B136" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C136" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D136" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E136" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F136" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G136" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H136" s="1">
         <v>295</v>
@@ -9135,25 +9222,25 @@
     </row>
     <row r="137" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B137" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C137" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D137" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E137" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F137" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G137" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H137" s="1">
         <v>480</v>
@@ -9186,22 +9273,22 @@
     </row>
     <row r="138" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B138" s="7">
         <v>46288.70853009259</v>
       </c>
       <c r="C138" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D138" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F138" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G138" t="s">
         <v>91</v>
@@ -9243,25 +9330,25 @@
     </row>
     <row r="139" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B139" s="7">
         <v>46289.572893518518</v>
       </c>
       <c r="C139" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D139" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E139" t="s">
         <v>57</v>
       </c>
       <c r="F139" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G139" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H139" s="1">
         <v>90</v>
@@ -9300,25 +9387,25 @@
     </row>
     <row r="140" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B140" s="7">
         <v>46289.569641203707</v>
       </c>
       <c r="C140" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D140" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E140" t="s">
         <v>61</v>
       </c>
       <c r="F140" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G140" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H140" s="1">
         <v>200</v>
@@ -9357,22 +9444,22 @@
     </row>
     <row r="141" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B141" s="7">
         <v>46289.567453703705</v>
       </c>
       <c r="C141" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D141" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E141" t="s">
         <v>57</v>
       </c>
       <c r="F141" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G141" t="s">
         <v>69</v>
@@ -9414,25 +9501,25 @@
     </row>
     <row r="142" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B142" s="7">
         <v>46289.571481481478</v>
       </c>
       <c r="C142" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D142" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E142" t="s">
         <v>116</v>
       </c>
       <c r="F142" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G142" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H142" s="1">
         <v>40</v>
@@ -9471,25 +9558,25 @@
     </row>
     <row r="143" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B143" s="7">
         <v>46289.718541666669</v>
       </c>
       <c r="C143" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D143" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E143" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F143" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G143" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H143" s="1">
         <v>135</v>
@@ -9528,25 +9615,25 @@
     </row>
     <row r="144" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B144" s="7">
         <v>46289.718541666669</v>
       </c>
       <c r="C144" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D144" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E144" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F144" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G144" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H144" s="1">
         <v>500</v>
@@ -9585,760 +9672,760 @@
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B145" s="7">
-        <v>46296.377858796295</v>
+        <v>46290.663263888891</v>
       </c>
       <c r="C145" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D145" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="E145" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="F145" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="G145" t="s">
-        <v>196</v>
+        <v>33</v>
       </c>
       <c r="H145" s="1">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="I145" s="8">
-        <v>70.91</v>
+        <v>40.28</v>
       </c>
       <c r="J145" s="8">
-        <v>14182</v>
+        <v>2618.1999999999998</v>
       </c>
       <c r="K145" s="1">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="L145" s="8">
-        <v>66</v>
+        <v>36.659999999999997</v>
       </c>
       <c r="M145" s="8">
-        <v>39600</v>
+        <v>3299.4</v>
       </c>
       <c r="N145" s="1">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="O145" s="8">
-        <v>63.48</v>
+        <v>33.51</v>
       </c>
       <c r="P145" s="8">
-        <v>63480</v>
+        <v>4021.2</v>
       </c>
       <c r="Q145" s="8">
         <v>0</v>
       </c>
       <c r="R145" s="8">
-        <v>39087.33</v>
+        <v>3312.93</v>
       </c>
       <c r="V145" s="7"/>
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B146" s="7">
-        <v>46296.377858796295</v>
+        <v>46290.663263888891</v>
       </c>
       <c r="C146" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D146" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="E146" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="F146" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="G146" t="s">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="H146" s="1">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="I146" s="8">
-        <v>16.7</v>
+        <v>56.64</v>
       </c>
       <c r="J146" s="8">
-        <v>8350</v>
+        <v>3681.6</v>
       </c>
       <c r="K146" s="1">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="L146" s="8">
-        <v>16.52</v>
+        <v>51.96</v>
       </c>
       <c r="M146" s="8">
-        <v>16520</v>
+        <v>4676.3999999999996</v>
       </c>
       <c r="N146" s="1">
-        <v>2000</v>
+        <v>120</v>
       </c>
       <c r="O146" s="8">
-        <v>15.8</v>
+        <v>47.74</v>
       </c>
       <c r="P146" s="8">
-        <v>31600</v>
+        <v>5728.8</v>
       </c>
       <c r="Q146" s="8">
         <v>0</v>
       </c>
       <c r="R146" s="8">
-        <v>3363.85</v>
+        <v>3312.93</v>
       </c>
       <c r="V146" s="7"/>
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B147" s="7">
-        <v>46290.663263888891</v>
+        <v>46295.710763888892</v>
       </c>
       <c r="C147" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D147" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="E147" t="s">
-        <v>370</v>
+        <v>170</v>
       </c>
       <c r="F147" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="G147" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H147" s="1">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I147" s="8">
-        <v>40.28</v>
+        <v>47.26</v>
       </c>
       <c r="J147" s="8">
-        <v>2618.1999999999998</v>
+        <v>2835.6</v>
       </c>
       <c r="K147" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L147" s="8">
-        <v>36.659999999999997</v>
+        <v>41.45</v>
       </c>
       <c r="M147" s="8">
-        <v>3299.4</v>
+        <v>3316</v>
       </c>
       <c r="N147" s="1">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="O147" s="8">
-        <v>33.51</v>
+        <v>36.51</v>
       </c>
       <c r="P147" s="8">
-        <v>4021.2</v>
+        <v>4016.1</v>
       </c>
       <c r="Q147" s="8">
         <v>0</v>
       </c>
       <c r="R147" s="8">
-        <v>3312.93</v>
+        <v>3389.23</v>
       </c>
       <c r="V147" s="7"/>
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B148" s="7">
-        <v>46290.663263888891</v>
+        <v>46294.695925925924</v>
       </c>
       <c r="C148" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="D148" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="E148" t="s">
-        <v>370</v>
+        <v>165</v>
       </c>
       <c r="F148" t="s">
-        <v>371</v>
-      </c>
-      <c r="G148" t="s">
-        <v>63</v>
+        <v>379</v>
       </c>
       <c r="H148" s="1">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I148" s="8">
-        <v>56.64</v>
+        <v>22.51</v>
       </c>
       <c r="J148" s="8">
-        <v>3681.6</v>
+        <v>1620.72</v>
       </c>
       <c r="K148" s="1">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L148" s="8">
-        <v>51.96</v>
+        <v>0</v>
       </c>
       <c r="M148" s="8">
-        <v>4676.3999999999996</v>
+        <v>0</v>
       </c>
       <c r="N148" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="O148" s="8">
-        <v>47.74</v>
+        <v>0</v>
       </c>
       <c r="P148" s="8">
-        <v>5728.8</v>
+        <v>0</v>
       </c>
       <c r="Q148" s="8">
         <v>0</v>
       </c>
       <c r="R148" s="8">
-        <v>3312.93</v>
+        <v>1620.72</v>
       </c>
       <c r="V148" s="7"/>
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B149" s="7">
-        <v>46295.710763888892</v>
+        <v>46295.662303240744</v>
       </c>
       <c r="C149" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="D149" t="s">
-        <v>27</v>
+        <v>255</v>
       </c>
       <c r="E149" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F149" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="G149" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="H149" s="1">
         <v>60</v>
       </c>
       <c r="I149" s="8">
-        <v>47.26</v>
+        <v>52.34</v>
       </c>
       <c r="J149" s="8">
-        <v>2835.6</v>
+        <v>3140.4</v>
       </c>
       <c r="K149" s="1">
         <v>80</v>
       </c>
       <c r="L149" s="8">
-        <v>41.45</v>
+        <v>47.46</v>
       </c>
       <c r="M149" s="8">
-        <v>3316</v>
+        <v>3796.8</v>
       </c>
       <c r="N149" s="1">
         <v>110</v>
       </c>
       <c r="O149" s="8">
-        <v>36.51</v>
+        <v>42.38</v>
       </c>
       <c r="P149" s="8">
-        <v>4016.1</v>
+        <v>4661.8</v>
       </c>
       <c r="Q149" s="8">
         <v>0</v>
       </c>
       <c r="R149" s="8">
-        <v>3389.23</v>
+        <v>3866.33</v>
       </c>
       <c r="V149" s="7"/>
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B150" s="7">
-        <v>46294.695925925924</v>
+        <v>46295.662303240744</v>
       </c>
       <c r="C150" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D150" t="s">
-        <v>27</v>
+        <v>255</v>
       </c>
       <c r="E150" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="F150" t="s">
-        <v>377</v>
+        <v>383</v>
+      </c>
+      <c r="G150" t="s">
+        <v>33</v>
       </c>
       <c r="H150" s="1">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="I150" s="8">
-        <v>22.51</v>
+        <v>134.30000000000001</v>
       </c>
       <c r="J150" s="8">
-        <v>1620.72</v>
+        <v>3357.5</v>
       </c>
       <c r="K150" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L150" s="8">
-        <v>0</v>
+        <v>119.02</v>
       </c>
       <c r="M150" s="8">
-        <v>0</v>
+        <v>4165.7</v>
       </c>
       <c r="N150" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O150" s="8">
-        <v>0</v>
+        <v>106.27</v>
       </c>
       <c r="P150" s="8">
-        <v>0</v>
+        <v>5313.5</v>
       </c>
       <c r="Q150" s="8">
         <v>0</v>
       </c>
       <c r="R150" s="8">
-        <v>1620.72</v>
+        <v>4278.8999999999996</v>
       </c>
       <c r="V150" s="7"/>
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B151" s="7">
         <v>46295.662303240744</v>
       </c>
       <c r="C151" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D151" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E151" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F151" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G151" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H151" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I151" s="8">
-        <v>52.34</v>
+        <v>103.78</v>
       </c>
       <c r="J151" s="8">
-        <v>3140.4</v>
+        <v>3113.4</v>
       </c>
       <c r="K151" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L151" s="8">
-        <v>47.46</v>
+        <v>86.34</v>
       </c>
       <c r="M151" s="8">
-        <v>3796.8</v>
+        <v>3453.6</v>
       </c>
       <c r="N151" s="1">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="O151" s="8">
-        <v>42.38</v>
+        <v>72.33</v>
       </c>
       <c r="P151" s="8">
-        <v>4661.8</v>
+        <v>3978.15</v>
       </c>
       <c r="Q151" s="8">
         <v>0</v>
       </c>
       <c r="R151" s="8">
-        <v>3866.33</v>
+        <v>3515.05</v>
       </c>
       <c r="V151" s="7"/>
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B152" s="7">
-        <v>46295.662303240744</v>
+        <v>46295.662824074076</v>
       </c>
       <c r="C152" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D152" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E152" t="s">
-        <v>173</v>
+        <v>387</v>
       </c>
       <c r="F152" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="G152" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H152" s="1">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I152" s="8">
-        <v>134.30000000000001</v>
+        <v>47.23</v>
       </c>
       <c r="J152" s="8">
-        <v>3357.5</v>
+        <v>2833.8</v>
       </c>
       <c r="K152" s="1">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="L152" s="8">
-        <v>119.02</v>
+        <v>43.38</v>
       </c>
       <c r="M152" s="8">
-        <v>4165.7</v>
+        <v>3470.4</v>
       </c>
       <c r="N152" s="1">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="O152" s="8">
-        <v>106.27</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="P152" s="8">
-        <v>5313.5</v>
+        <v>4339.5</v>
       </c>
       <c r="Q152" s="8">
         <v>0</v>
       </c>
       <c r="R152" s="8">
-        <v>4278.8999999999996</v>
+        <v>3547.9</v>
       </c>
       <c r="V152" s="7"/>
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B153" s="7">
-        <v>46295.662303240744</v>
+        <v>46295.662824074076</v>
       </c>
       <c r="C153" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D153" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E153" t="s">
-        <v>173</v>
+        <v>387</v>
       </c>
       <c r="F153" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G153" t="s">
         <v>63</v>
       </c>
       <c r="H153" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I153" s="8">
-        <v>103.78</v>
+        <v>64.86</v>
       </c>
       <c r="J153" s="8">
-        <v>3113.4</v>
+        <v>3243</v>
       </c>
       <c r="K153" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="L153" s="8">
-        <v>86.34</v>
+        <v>54.04</v>
       </c>
       <c r="M153" s="8">
-        <v>3453.6</v>
+        <v>5404</v>
       </c>
       <c r="N153" s="1">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="O153" s="8">
-        <v>72.33</v>
+        <v>49.96</v>
       </c>
       <c r="P153" s="8">
-        <v>3978.15</v>
+        <v>7494</v>
       </c>
       <c r="Q153" s="8">
         <v>0</v>
       </c>
       <c r="R153" s="8">
-        <v>3515.05</v>
+        <v>5380.33</v>
       </c>
       <c r="V153" s="7"/>
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B154" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C154" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D154" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E154" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F154" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G154" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H154" s="1">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="I154" s="8">
-        <v>47.23</v>
+        <v>13.02</v>
       </c>
       <c r="J154" s="8">
-        <v>2833.8</v>
+        <v>2734.2</v>
       </c>
       <c r="K154" s="1">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="L154" s="8">
-        <v>43.38</v>
+        <v>11.67</v>
       </c>
       <c r="M154" s="8">
-        <v>3470.4</v>
+        <v>3267.6</v>
       </c>
       <c r="N154" s="1">
-        <v>110</v>
+        <v>375</v>
       </c>
       <c r="O154" s="8">
-        <v>39.450000000000003</v>
+        <v>10.57</v>
       </c>
       <c r="P154" s="8">
-        <v>4339.5</v>
+        <v>3963.75</v>
       </c>
       <c r="Q154" s="8">
         <v>0</v>
       </c>
       <c r="R154" s="8">
-        <v>3547.9</v>
+        <v>3321.85</v>
       </c>
       <c r="V154" s="7"/>
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B155" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C155" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D155" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E155" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F155" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G155" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="H155" s="1">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="I155" s="8">
-        <v>64.86</v>
+        <v>19.670000000000002</v>
       </c>
       <c r="J155" s="8">
-        <v>3243</v>
+        <v>2753.8</v>
       </c>
       <c r="K155" s="1">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="L155" s="8">
-        <v>54.04</v>
+        <v>17.68</v>
       </c>
       <c r="M155" s="8">
-        <v>5404</v>
+        <v>3359.2</v>
       </c>
       <c r="N155" s="1">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="O155" s="8">
-        <v>49.96</v>
+        <v>16.12</v>
       </c>
       <c r="P155" s="8">
-        <v>7494</v>
+        <v>4110.6000000000004</v>
       </c>
       <c r="Q155" s="8">
         <v>0</v>
       </c>
       <c r="R155" s="8">
-        <v>5380.33</v>
+        <v>3407.87</v>
       </c>
       <c r="V155" s="7"/>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B156" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C156" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D156" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E156" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F156" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G156" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="H156" s="1">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="I156" s="8">
-        <v>13.02</v>
+        <v>102.9</v>
       </c>
       <c r="J156" s="8">
-        <v>2734.2</v>
+        <v>5145</v>
       </c>
       <c r="K156" s="1">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="L156" s="8">
-        <v>11.67</v>
+        <v>96.4</v>
       </c>
       <c r="M156" s="8">
-        <v>3267.6</v>
+        <v>9640</v>
       </c>
       <c r="N156" s="1">
-        <v>375</v>
+        <v>150</v>
       </c>
       <c r="O156" s="8">
-        <v>10.57</v>
+        <v>88.06</v>
       </c>
       <c r="P156" s="8">
-        <v>3963.75</v>
+        <v>13209</v>
       </c>
       <c r="Q156" s="8">
         <v>0</v>
       </c>
       <c r="R156" s="8">
-        <v>3321.85</v>
+        <v>9331.33</v>
       </c>
       <c r="V156" s="7"/>
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B157" s="7">
-        <v>46295.662824074076</v>
+        <v>46295.660590277781</v>
       </c>
       <c r="C157" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D157" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E157" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F157" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G157" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H157" s="1">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="I157" s="8">
-        <v>19.670000000000002</v>
+        <v>42.35</v>
       </c>
       <c r="J157" s="8">
-        <v>2753.8</v>
+        <v>4235</v>
       </c>
       <c r="K157" s="1">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="L157" s="8">
-        <v>17.68</v>
+        <v>37.42</v>
       </c>
       <c r="M157" s="8">
-        <v>3359.2</v>
+        <v>5613</v>
       </c>
       <c r="N157" s="1">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="O157" s="8">
-        <v>16.12</v>
+        <v>34.270000000000003</v>
       </c>
       <c r="P157" s="8">
-        <v>4110.6000000000004</v>
+        <v>6854</v>
       </c>
       <c r="Q157" s="8">
         <v>0</v>
       </c>
       <c r="R157" s="8">
-        <v>3407.87</v>
+        <v>5567.33</v>
       </c>
       <c r="V157" s="7"/>
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B158" s="7">
-        <v>46295.662824074076</v>
+        <v>46295.660590277781</v>
       </c>
       <c r="C158" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D158" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E158" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F158" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G158" t="s">
         <v>63</v>
@@ -10347,719 +10434,666 @@
         <v>50</v>
       </c>
       <c r="I158" s="8">
-        <v>102.9</v>
+        <v>68.58</v>
       </c>
       <c r="J158" s="8">
-        <v>5145</v>
+        <v>3429</v>
       </c>
       <c r="K158" s="1">
         <v>100</v>
       </c>
       <c r="L158" s="8">
-        <v>96.4</v>
+        <v>53.92</v>
       </c>
       <c r="M158" s="8">
-        <v>9640</v>
+        <v>5392</v>
       </c>
       <c r="N158" s="1">
         <v>150</v>
       </c>
       <c r="O158" s="8">
-        <v>88.06</v>
+        <v>48.38</v>
       </c>
       <c r="P158" s="8">
-        <v>13209</v>
+        <v>7257</v>
       </c>
       <c r="Q158" s="8">
         <v>0</v>
       </c>
       <c r="R158" s="8">
-        <v>9331.33</v>
+        <v>5359.33</v>
       </c>
       <c r="V158" s="7"/>
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B159" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C159" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D159" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E159" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F159" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G159" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="H159" s="1">
+        <v>75</v>
+      </c>
+      <c r="I159" s="8">
+        <v>36.72</v>
+      </c>
+      <c r="J159" s="8">
+        <v>2754</v>
+      </c>
+      <c r="K159" s="1">
         <v>100</v>
       </c>
-      <c r="I159" s="8">
-        <v>42.35</v>
-      </c>
-      <c r="J159" s="8">
-        <v>4235</v>
-      </c>
-      <c r="K159" s="1">
-        <v>150</v>
-      </c>
       <c r="L159" s="8">
-        <v>37.42</v>
+        <v>33.32</v>
       </c>
       <c r="M159" s="8">
-        <v>5613</v>
+        <v>3332</v>
       </c>
       <c r="N159" s="1">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="O159" s="8">
-        <v>34.270000000000003</v>
+        <v>31.7</v>
       </c>
       <c r="P159" s="8">
-        <v>6854</v>
+        <v>4279.5</v>
       </c>
       <c r="Q159" s="8">
         <v>0</v>
       </c>
       <c r="R159" s="8">
-        <v>5567.33</v>
+        <v>3455.17</v>
       </c>
       <c r="V159" s="7"/>
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B160" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C160" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D160" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E160" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F160" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G160" t="s">
-        <v>63</v>
+        <v>398</v>
       </c>
       <c r="H160" s="1">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="I160" s="8">
-        <v>68.58</v>
+        <v>24.71</v>
       </c>
       <c r="J160" s="8">
-        <v>3429</v>
+        <v>3212.3</v>
       </c>
       <c r="K160" s="1">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="L160" s="8">
-        <v>53.92</v>
+        <v>21.81</v>
       </c>
       <c r="M160" s="8">
-        <v>5392</v>
+        <v>3816.75</v>
       </c>
       <c r="N160" s="1">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="O160" s="8">
-        <v>48.38</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="P160" s="8">
-        <v>7257</v>
+        <v>4601.3</v>
       </c>
       <c r="Q160" s="8">
         <v>0</v>
       </c>
       <c r="R160" s="8">
-        <v>5359.33</v>
+        <v>3876.78</v>
       </c>
       <c r="V160" s="7"/>
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B161" s="7">
-        <v>46295.660590277781</v>
+        <v>46295.67895833333</v>
       </c>
       <c r="C161" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="D161" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E161" t="s">
-        <v>385</v>
+        <v>137</v>
       </c>
       <c r="F161" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="G161" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="H161" s="1">
+        <v>40</v>
+      </c>
+      <c r="I161" s="8">
+        <v>70.12</v>
+      </c>
+      <c r="J161" s="8">
+        <v>2804.8</v>
+      </c>
+      <c r="K161" s="1">
+        <v>55</v>
+      </c>
+      <c r="L161" s="8">
+        <v>56.96</v>
+      </c>
+      <c r="M161" s="8">
+        <v>3132.8</v>
+      </c>
+      <c r="N161" s="1">
         <v>75</v>
       </c>
-      <c r="I161" s="8">
-        <v>36.72</v>
-      </c>
-      <c r="J161" s="8">
-        <v>2754</v>
-      </c>
-      <c r="K161" s="1">
-        <v>100</v>
-      </c>
-      <c r="L161" s="8">
-        <v>33.32</v>
-      </c>
-      <c r="M161" s="8">
-        <v>3332</v>
-      </c>
-      <c r="N161" s="1">
-        <v>135</v>
-      </c>
       <c r="O161" s="8">
-        <v>31.7</v>
+        <v>47.9</v>
       </c>
       <c r="P161" s="8">
-        <v>4279.5</v>
+        <v>3592.5</v>
       </c>
       <c r="Q161" s="8">
         <v>0</v>
       </c>
       <c r="R161" s="8">
-        <v>3455.17</v>
+        <v>3176.7</v>
       </c>
       <c r="V161" s="7"/>
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B162" s="7">
-        <v>46295.660590277781</v>
+        <v>46295.67895833333</v>
       </c>
       <c r="C162" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="D162" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E162" t="s">
-        <v>385</v>
+        <v>137</v>
       </c>
       <c r="F162" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="G162" t="s">
-        <v>396</v>
+        <v>69</v>
       </c>
       <c r="H162" s="1">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="I162" s="8">
-        <v>24.71</v>
+        <v>85.86</v>
       </c>
       <c r="J162" s="8">
-        <v>3212.3</v>
+        <v>3005.1</v>
       </c>
       <c r="K162" s="1">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="L162" s="8">
-        <v>21.81</v>
+        <v>77.540000000000006</v>
       </c>
       <c r="M162" s="8">
-        <v>3816.75</v>
+        <v>3877</v>
       </c>
       <c r="N162" s="1">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="O162" s="8">
-        <v>19.579999999999998</v>
+        <v>70.56</v>
       </c>
       <c r="P162" s="8">
-        <v>4601.3</v>
+        <v>4939.2</v>
       </c>
       <c r="Q162" s="8">
         <v>0</v>
       </c>
       <c r="R162" s="8">
-        <v>3876.78</v>
+        <v>3940.43</v>
       </c>
       <c r="V162" s="7"/>
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B163" s="7">
         <v>46295.67895833333</v>
       </c>
       <c r="C163" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D163" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E163" t="s">
         <v>137</v>
       </c>
       <c r="F163" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G163" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H163" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I163" s="8">
-        <v>70.12</v>
+        <v>27.49</v>
       </c>
       <c r="J163" s="8">
-        <v>2804.8</v>
+        <v>2749</v>
       </c>
       <c r="K163" s="1">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="L163" s="8">
-        <v>56.96</v>
+        <v>22.26</v>
       </c>
       <c r="M163" s="8">
-        <v>3132.8</v>
+        <v>3005.1</v>
       </c>
       <c r="N163" s="1">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="O163" s="8">
-        <v>47.9</v>
+        <v>18.54</v>
       </c>
       <c r="P163" s="8">
-        <v>3592.5</v>
+        <v>3337.2</v>
       </c>
       <c r="Q163" s="8">
         <v>0</v>
       </c>
       <c r="R163" s="8">
-        <v>3176.7</v>
+        <v>3030.43</v>
       </c>
       <c r="V163" s="7"/>
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B164" s="7">
-        <v>46295.67895833333</v>
+        <v>46295.671307870369</v>
       </c>
       <c r="C164" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="D164" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E164" t="s">
-        <v>137</v>
+        <v>387</v>
       </c>
       <c r="F164" t="s">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="G164" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="H164" s="1">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="I164" s="8">
-        <v>85.86</v>
+        <v>31.24</v>
       </c>
       <c r="J164" s="8">
-        <v>3005.1</v>
+        <v>3124</v>
       </c>
       <c r="K164" s="1">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L164" s="8">
-        <v>77.540000000000006</v>
+        <v>28.47</v>
       </c>
       <c r="M164" s="8">
-        <v>3877</v>
+        <v>4270.5</v>
       </c>
       <c r="N164" s="1">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="O164" s="8">
-        <v>70.56</v>
+        <v>25.76</v>
       </c>
       <c r="P164" s="8">
-        <v>4939.2</v>
+        <v>5152</v>
       </c>
       <c r="Q164" s="8">
         <v>0</v>
       </c>
       <c r="R164" s="8">
-        <v>3940.43</v>
+        <v>4182.17</v>
       </c>
       <c r="V164" s="7"/>
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B165" s="7">
-        <v>46295.67895833333</v>
+        <v>46295.671307870369</v>
       </c>
       <c r="C165" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="D165" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E165" t="s">
-        <v>137</v>
+        <v>387</v>
       </c>
       <c r="F165" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="G165" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="H165" s="1">
+        <v>50</v>
+      </c>
+      <c r="I165" s="8">
+        <v>170.83</v>
+      </c>
+      <c r="J165" s="8">
+        <v>8541.5</v>
+      </c>
+      <c r="K165" s="1">
         <v>100</v>
       </c>
-      <c r="I165" s="8">
-        <v>27.49</v>
-      </c>
-      <c r="J165" s="8">
-        <v>2749</v>
-      </c>
-      <c r="K165" s="1">
-        <v>135</v>
-      </c>
       <c r="L165" s="8">
-        <v>22.26</v>
+        <v>148.03</v>
       </c>
       <c r="M165" s="8">
-        <v>3005.1</v>
+        <v>14803</v>
       </c>
       <c r="N165" s="1">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="O165" s="8">
-        <v>18.54</v>
+        <v>140.21</v>
       </c>
       <c r="P165" s="8">
-        <v>3337.2</v>
+        <v>21031.5</v>
       </c>
       <c r="Q165" s="8">
         <v>0</v>
       </c>
       <c r="R165" s="8">
-        <v>3030.43</v>
+        <v>14792</v>
       </c>
       <c r="V165" s="7"/>
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B166" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C166" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D166" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E166" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F166" t="s">
-        <v>179</v>
+        <v>407</v>
       </c>
       <c r="G166" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H166" s="1">
+        <v>50</v>
+      </c>
+      <c r="I166" s="8">
+        <v>108.32</v>
+      </c>
+      <c r="J166" s="8">
+        <v>5416</v>
+      </c>
+      <c r="K166" s="1">
         <v>100</v>
       </c>
-      <c r="I166" s="8">
-        <v>31.24</v>
-      </c>
-      <c r="J166" s="8">
-        <v>3124</v>
-      </c>
-      <c r="K166" s="1">
+      <c r="L166" s="8">
+        <v>87.79</v>
+      </c>
+      <c r="M166" s="8">
+        <v>8779</v>
+      </c>
+      <c r="N166" s="1">
         <v>150</v>
       </c>
-      <c r="L166" s="8">
-        <v>28.47</v>
-      </c>
-      <c r="M166" s="8">
-        <v>4270.5</v>
-      </c>
-      <c r="N166" s="1">
-        <v>200</v>
-      </c>
       <c r="O166" s="8">
-        <v>25.76</v>
+        <v>76.010000000000005</v>
       </c>
       <c r="P166" s="8">
-        <v>5152</v>
+        <v>11401.5</v>
       </c>
       <c r="Q166" s="8">
         <v>0</v>
       </c>
       <c r="R166" s="8">
-        <v>4182.17</v>
+        <v>8532.17</v>
       </c>
       <c r="V166" s="7"/>
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B167" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C167" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D167" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E167" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F167" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="G167" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="H167" s="1">
         <v>50</v>
       </c>
       <c r="I167" s="8">
-        <v>170.83</v>
+        <v>100.49</v>
       </c>
       <c r="J167" s="8">
-        <v>8541.5</v>
+        <v>5024.5</v>
       </c>
       <c r="K167" s="1">
         <v>100</v>
       </c>
       <c r="L167" s="8">
-        <v>148.03</v>
+        <v>86.37</v>
       </c>
       <c r="M167" s="8">
-        <v>14803</v>
+        <v>8637</v>
       </c>
       <c r="N167" s="1">
         <v>150</v>
       </c>
       <c r="O167" s="8">
-        <v>140.21</v>
+        <v>80.64</v>
       </c>
       <c r="P167" s="8">
-        <v>21031.5</v>
+        <v>12096</v>
       </c>
       <c r="Q167" s="8">
         <v>0</v>
       </c>
       <c r="R167" s="8">
-        <v>14792</v>
+        <v>8585.83</v>
       </c>
       <c r="V167" s="7"/>
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B168" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C168" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D168" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E168" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F168" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G168" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="H168" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I168" s="8">
-        <v>108.32</v>
+        <v>192.82</v>
       </c>
       <c r="J168" s="8">
-        <v>5416</v>
+        <v>5784.6</v>
       </c>
       <c r="K168" s="1">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="L168" s="8">
-        <v>87.79</v>
+        <v>167.24</v>
       </c>
       <c r="M168" s="8">
-        <v>8779</v>
+        <v>7525.8</v>
       </c>
       <c r="N168" s="1">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="O168" s="8">
-        <v>76.010000000000005</v>
+        <v>151.91999999999999</v>
       </c>
       <c r="P168" s="8">
-        <v>11401.5</v>
+        <v>9115.2000000000007</v>
       </c>
       <c r="Q168" s="8">
         <v>0</v>
       </c>
       <c r="R168" s="8">
-        <v>8532.17</v>
+        <v>7475.2</v>
       </c>
       <c r="V168" s="7"/>
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B169" s="7">
-        <v>46295.671307870369</v>
+        <v>46296.652222222219</v>
       </c>
       <c r="C169" t="s">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="D169" t="s">
-        <v>253</v>
+        <v>56</v>
       </c>
       <c r="E169" t="s">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="F169" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="G169" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="H169" s="1">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="I169" s="8">
-        <v>100.49</v>
+        <v>62.94</v>
       </c>
       <c r="J169" s="8">
-        <v>5024.5</v>
+        <v>62940</v>
       </c>
       <c r="K169" s="1">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="L169" s="8">
-        <v>86.37</v>
+        <v>62.05</v>
       </c>
       <c r="M169" s="8">
-        <v>8637</v>
+        <v>93075</v>
       </c>
       <c r="N169" s="1">
-        <v>150</v>
+        <v>2000</v>
       </c>
       <c r="O169" s="8">
-        <v>80.64</v>
+        <v>60.16</v>
       </c>
       <c r="P169" s="8">
-        <v>12096</v>
+        <v>120320</v>
       </c>
       <c r="Q169" s="8">
         <v>0</v>
       </c>
       <c r="R169" s="8">
-        <v>8585.83</v>
+        <v>92111.67</v>
       </c>
       <c r="V169" s="7"/>
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>402</v>
-      </c>
-      <c r="B170" s="7">
-        <v>46295.671307870369</v>
-      </c>
-      <c r="C170" t="s">
-        <v>403</v>
-      </c>
-      <c r="D170" t="s">
-        <v>253</v>
-      </c>
-      <c r="E170" t="s">
-        <v>385</v>
-      </c>
-      <c r="F170" t="s">
-        <v>407</v>
-      </c>
-      <c r="G170" t="s">
-        <v>30</v>
-      </c>
-      <c r="H170" s="1">
-        <v>30</v>
-      </c>
-      <c r="I170" s="8">
-        <v>192.82</v>
-      </c>
-      <c r="J170" s="8">
-        <v>5784.6</v>
-      </c>
-      <c r="K170" s="1">
-        <v>45</v>
-      </c>
-      <c r="L170" s="8">
-        <v>167.24</v>
-      </c>
-      <c r="M170" s="8">
-        <v>7525.8</v>
-      </c>
-      <c r="N170" s="1">
-        <v>60</v>
-      </c>
-      <c r="O170" s="8">
-        <v>151.91999999999999</v>
-      </c>
-      <c r="P170" s="8">
-        <v>9115.2000000000007</v>
-      </c>
-      <c r="Q170" s="8">
-        <v>0</v>
-      </c>
-      <c r="R170" s="8">
-        <v>7475.2</v>
-      </c>
+      <c r="B170" s="7"/>
       <c r="V170" s="7"/>
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.25">
@@ -11830,19 +11864,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{952A4A4C-4AC7-4023-A366-C6C9C6518A26}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{5E09103F-18DA-41D8-AADC-051314F72875}">
       <formula1>"Preço, Prazo de entrega, Condição de Pagamento, Quantidade, Sem Retorno, Optou por outro produto"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{CA83D359-D511-4382-A273-83915D3682AF}">
+    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{A64244E1-75E5-47BB-97FC-337746BC6580}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{E1BE5EAA-4451-420F-872A-2FDA0A091895}">
+    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{A8596BA2-E648-420A-AD3D-9C5FC00EE59F}">
       <formula1>"AC,AL,AP,AM,BA,CE,DF,ES,GO,MA,MT,MS,MG,PA,PB,PR,PE,PI,RJ,RN,RS,RO,RR,SC,SP,SE,TO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{BE469C24-F4C9-4FBA-A446-BDC6B572EEBF}">
+    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{3DAD7F24-4560-47CE-A770-E0B61F91C11C}">
       <formula1>"Mínima,2ª Opção,3ª Opção,-"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{1BE40708-CD39-45D8-8B72-827AD5F2EC60}">
+    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{060C5511-3C88-4FF3-A683-017CD1ACCE6F}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,Rascunho"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Base_Orcamentos.xlsx
+++ b/Base_Orcamentos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Orcamento\CONTROLE DE ORÇAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A9698F-F80F-455D-8756-5B13C1A1B577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D6D0CAE-A8D5-49A7-B9F1-E572334D1DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{495ACB26-57DB-4BC2-9659-FD6F45A21599}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{035846D1-255F-4666-8D29-8D700277EFF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Orcamentos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base_Orcamentos!$A$2:$W$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base_Orcamentos!$A$2:$X$169</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="451">
   <si>
     <t>Nº Orçamento</t>
   </si>
@@ -194,6 +194,9 @@
     <t>A.73 BOPP Branco Brilho</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
     <t>ORC 26080506</t>
   </si>
   <si>
@@ -320,6 +323,12 @@
     <t>A.08 Papel Couchê</t>
   </si>
   <si>
+    <t>Perdido</t>
+  </si>
+  <si>
+    <t>Preço</t>
+  </si>
+  <si>
     <t>ORC 26081009</t>
   </si>
   <si>
@@ -464,9 +473,6 @@
     <t>R.14 TÉRMICO 72G DRY</t>
   </si>
   <si>
-    <t>Aprovado</t>
-  </si>
-  <si>
     <t>ORC 26081902</t>
   </si>
   <si>
@@ -620,9 +626,6 @@
     <t>ROT 75mm X 50mm X 1 C | 45 M  c/ 840 ETIQ</t>
   </si>
   <si>
-    <t>Perdido</t>
-  </si>
-  <si>
     <t>Condição de Pagamento</t>
   </si>
   <si>
@@ -1278,6 +1281,120 @@
   </si>
   <si>
     <t>ETIQ 85mm X 32mm X 1 C | 175 M  c/ 5000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100201</t>
+  </si>
+  <si>
+    <t>ETIQ 43,17mm X 51,32mm X 1 C | 23,5 M  c/ 420 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100204</t>
+  </si>
+  <si>
+    <t>FERREIRAMED</t>
+  </si>
+  <si>
+    <t>SÉRGIO</t>
+  </si>
+  <si>
+    <t>ETIQ 50mm X 30mm X 1 C | 33 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ROT 50mm X 30mm X 1 C | 16,5 M  c/ 500 ROT</t>
+  </si>
+  <si>
+    <t>ETIQ 33mm X 21mm X 3 C | 30 M  c/ 1250 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100208</t>
+  </si>
+  <si>
+    <t>LÍDER COMÉRCIO</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>ANDERSON</t>
+  </si>
+  <si>
+    <t>ETIQ 79mm X 95mm X 1 C | 45 M  c/ 450 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100501</t>
+  </si>
+  <si>
+    <t>GW PRIME COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>ETIQ 50mm X 30mm X 2 C | 49,5 M  c/ 3000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100502</t>
+  </si>
+  <si>
+    <t>CAPS CORP COMERCIO DE ARTIGOS OPTICOS LTDA</t>
+  </si>
+  <si>
+    <t>ETIQ 40mm X 40mm X 1 C | 21,5 M  c/ 500 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100503</t>
+  </si>
+  <si>
+    <t>SUERMERCADO BOM LAMI</t>
+  </si>
+  <si>
+    <t>ETIQ 40mm X 60mm X 1 C | 63 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100504</t>
+  </si>
+  <si>
+    <t>MASSA PURA</t>
+  </si>
+  <si>
+    <t>ETIQ 60mm X 100mm X 1 C | 103 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100505</t>
+  </si>
+  <si>
+    <t>BAR ZENAIDE</t>
+  </si>
+  <si>
+    <t>ETIQ 60mm X 40mm X 1 C | 40 M  c/ 930 ETIQ</t>
+  </si>
+  <si>
+    <t>A.52 BOPP Térmico</t>
+  </si>
+  <si>
+    <t>ORC 26100506</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO DORENSE</t>
+  </si>
+  <si>
+    <t>GERALDO</t>
+  </si>
+  <si>
+    <t>ETIQ 60mm X 125mm X 1 C | 128 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>LACRE 90mm X 190mm X 1 C | 193 M  c/ 1000 LACRE</t>
+  </si>
+  <si>
+    <t>ORC 26100507</t>
+  </si>
+  <si>
+    <t>DOMENICHELLI</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ETIQ 65mm X 225mm X 1 C | 236 M  c/ 1030 ETIQ</t>
   </si>
 </sst>
 </file>
@@ -1285,8 +1402,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot;#,##0.00_);\(&quot;R$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="165" formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="7" formatCode="&quot;R$&quot;#,##0.00_);\(&quot;R$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1364,26 +1481,26 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1690,7 +1807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07452749-6F0B-425E-BFD1-336AFE831639}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B5D822-AABD-4EAF-B56D-791DC31203AF}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:X390"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1722,10 +1839,10 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q1" s="8">
-        <v>170894.7</v>
+        <v>178977.62</v>
       </c>
       <c r="R1" s="8">
-        <v>1364979.52</v>
+        <v>1494838.36</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="30" x14ac:dyDescent="0.25">
@@ -2125,31 +2242,37 @@
         <v>5428.92</v>
       </c>
       <c r="Q8" s="8">
-        <v>0</v>
+        <v>3160.99</v>
       </c>
       <c r="R8" s="8">
         <v>4198.6899999999996</v>
       </c>
+      <c r="S8" t="s">
+        <v>50</v>
+      </c>
+      <c r="T8" t="s">
+        <v>44</v>
+      </c>
       <c r="V8" s="7"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="7">
         <v>46239.674155092594</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
         <v>33</v>
@@ -2191,22 +2314,22 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="7">
         <v>46240.481354166666</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2248,25 +2371,25 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="7">
         <v>46240.65388888889</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H11" s="1">
         <v>1000</v>
@@ -2293,25 +2416,25 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="7">
         <v>46240.65388888889</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H12" s="1">
         <v>500</v>
@@ -2338,25 +2461,25 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" s="7">
         <v>46245.705243055556</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H13" s="1">
         <v>50</v>
@@ -2377,22 +2500,22 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="7">
         <v>46241.479583333334</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
         <v>33</v>
@@ -2434,13 +2557,13 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B15" s="7">
         <v>46254.398125</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
@@ -2449,10 +2572,10 @@
         <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="1">
         <v>10</v>
@@ -2491,13 +2614,13 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B16" s="7">
         <v>46245.441851851851</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
@@ -2506,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
         <v>29</v>
@@ -2548,13 +2671,13 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B17" s="7">
         <v>46245.441851851851</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -2563,7 +2686,7 @@
         <v>27</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s">
         <v>29</v>
@@ -2605,13 +2728,13 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" s="7">
         <v>46245.441851851851</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -2620,7 +2743,7 @@
         <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s">
         <v>29</v>
@@ -2662,13 +2785,13 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="7">
         <v>46245.441851851851</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -2677,10 +2800,10 @@
         <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H19" s="1">
         <v>100</v>
@@ -2719,13 +2842,13 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="7">
         <v>46245.441851851851</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
@@ -2734,7 +2857,7 @@
         <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s">
         <v>29</v>
@@ -2776,13 +2899,13 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="7">
         <v>46244.500115740739</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
@@ -2791,7 +2914,7 @@
         <v>47</v>
       </c>
       <c r="F21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s">
         <v>33</v>
@@ -2824,22 +2947,28 @@
         <v>4197.51</v>
       </c>
       <c r="Q21" s="8">
-        <v>0</v>
+        <v>2455.4899999999998</v>
       </c>
       <c r="R21" s="8">
         <v>3282.48</v>
       </c>
+      <c r="S21" t="s">
+        <v>50</v>
+      </c>
+      <c r="T21" t="s">
+        <v>44</v>
+      </c>
       <c r="V21" s="7"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="7">
         <v>46244.682013888887</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
@@ -2848,10 +2977,10 @@
         <v>47</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H22" s="1">
         <v>900</v>
@@ -2868,17 +2997,23 @@
       <c r="R22" s="8">
         <v>17888.37</v>
       </c>
+      <c r="S22" t="s">
+        <v>93</v>
+      </c>
+      <c r="U22" t="s">
+        <v>94</v>
+      </c>
       <c r="V22" s="7"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B23" s="7">
         <v>46244.715231481481</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
@@ -2887,10 +3022,10 @@
         <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H23" s="1">
         <v>100</v>
@@ -2929,13 +3064,13 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B24" s="7">
         <v>46245.668530092589</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
@@ -2944,10 +3079,10 @@
         <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H24" s="1">
         <v>15</v>
@@ -2986,13 +3121,13 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B25" s="7">
         <v>46245.668530092589</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
         <v>26</v>
@@ -3001,10 +3136,10 @@
         <v>27</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H25" s="1">
         <v>10</v>
@@ -3043,13 +3178,13 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B26" s="7">
         <v>46245.672835648147</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
@@ -3058,10 +3193,10 @@
         <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H26" s="1">
         <v>10</v>
@@ -3100,13 +3235,13 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B27" s="7">
         <v>46245.683391203704</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
@@ -3115,10 +3250,10 @@
         <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H27" s="1">
         <v>5</v>
@@ -3157,13 +3292,13 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B28" s="7">
         <v>46245.683391203704</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
@@ -3172,10 +3307,10 @@
         <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H28" s="1">
         <v>5</v>
@@ -3214,13 +3349,13 @@
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B29" s="7">
         <v>46245.683391203704</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
@@ -3229,10 +3364,10 @@
         <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H29" s="1">
         <v>5</v>
@@ -3271,13 +3406,13 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B30" s="7">
         <v>46245.68005787037</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
         <v>26</v>
@@ -3286,10 +3421,10 @@
         <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H30" s="1">
         <v>25</v>
@@ -3328,13 +3463,13 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B31" s="7">
         <v>46245.68005787037</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -3343,7 +3478,7 @@
         <v>27</v>
       </c>
       <c r="F31" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G31" t="s">
         <v>29</v>
@@ -3385,13 +3520,13 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B32" s="7">
         <v>46245.68005787037</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -3400,7 +3535,7 @@
         <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G32" t="s">
         <v>29</v>
@@ -3442,13 +3577,13 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B33" s="7">
         <v>46245.68005787037</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
         <v>26</v>
@@ -3457,10 +3592,10 @@
         <v>27</v>
       </c>
       <c r="F33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G33" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H33" s="1">
         <v>400</v>
@@ -3499,22 +3634,22 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B34" s="7">
         <v>46246.507789351854</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
         <v>26</v>
       </c>
       <c r="E34" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G34" t="s">
         <v>33</v>
@@ -3544,22 +3679,22 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B35" s="7">
         <v>46246.507789351854</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
         <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F35" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G35" t="s">
         <v>33</v>
@@ -3589,22 +3724,22 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B36" s="7">
         <v>46253.441805555558</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G36" t="s">
         <v>33</v>
@@ -3628,13 +3763,13 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B37" s="7">
         <v>46246.686018518521</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
         <v>26</v>
@@ -3643,10 +3778,10 @@
         <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G37" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H37" s="1">
         <v>95</v>
@@ -3676,22 +3811,28 @@
         <v>3992</v>
       </c>
       <c r="Q37" s="8">
-        <v>0</v>
+        <v>2466.44</v>
       </c>
       <c r="R37" s="8">
         <v>3182.24</v>
       </c>
+      <c r="S37" t="s">
+        <v>50</v>
+      </c>
+      <c r="T37" t="s">
+        <v>44</v>
+      </c>
       <c r="V37" s="7"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B38" s="7">
         <v>46247.492800925924</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
         <v>26</v>
@@ -3700,10 +3841,10 @@
         <v>47</v>
       </c>
       <c r="F38" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" t="s">
         <v>130</v>
-      </c>
-      <c r="G38" t="s">
-        <v>127</v>
       </c>
       <c r="H38" s="1">
         <v>100</v>
@@ -3720,29 +3861,32 @@
       <c r="R38" s="8">
         <v>1846.78</v>
       </c>
+      <c r="S38" t="s">
+        <v>43</v>
+      </c>
       <c r="V38" s="7"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B39" s="7">
         <v>46248.617152777777</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F39" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G39" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H39" s="1">
         <v>25</v>
@@ -3775,25 +3919,25 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B40" s="7">
         <v>46253.47934027778</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E40" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H40" s="1">
         <v>400</v>
@@ -3829,7 +3973,7 @@
         <v>4077.8</v>
       </c>
       <c r="S40" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="T40" t="s">
         <v>44</v>
@@ -3838,13 +3982,13 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B41" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
@@ -3853,7 +3997,7 @@
         <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G41" t="s">
         <v>49</v>
@@ -3895,13 +4039,13 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B42" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C42" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D42" t="s">
         <v>26</v>
@@ -3910,7 +4054,7 @@
         <v>27</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G42" t="s">
         <v>49</v>
@@ -3952,13 +4096,13 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B43" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D43" t="s">
         <v>26</v>
@@ -3967,7 +4111,7 @@
         <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G43" t="s">
         <v>49</v>
@@ -4009,13 +4153,13 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B44" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D44" t="s">
         <v>26</v>
@@ -4024,7 +4168,7 @@
         <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G44" t="s">
         <v>49</v>
@@ -4066,13 +4210,13 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B45" s="7">
         <v>46253.404016203705</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s">
         <v>26</v>
@@ -4081,7 +4225,7 @@
         <v>27</v>
       </c>
       <c r="F45" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G45" t="s">
         <v>49</v>
@@ -4123,13 +4267,13 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B46" s="7">
         <v>46253.684652777774</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D46" t="s">
         <v>26</v>
@@ -4138,10 +4282,10 @@
         <v>27</v>
       </c>
       <c r="F46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G46" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H46" s="1">
         <v>5</v>
@@ -4180,13 +4324,13 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B47" s="7">
         <v>46253.684652777774</v>
       </c>
       <c r="C47" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D47" t="s">
         <v>26</v>
@@ -4195,10 +4339,10 @@
         <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H47" s="1">
         <v>450</v>
@@ -4237,22 +4381,22 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B48" s="7">
         <v>46253.707175925927</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D48" t="s">
         <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F48" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G48" t="s">
         <v>29</v>
@@ -4300,25 +4444,25 @@
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B49" s="7">
         <v>46254.331678240742</v>
       </c>
       <c r="C49" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D49" t="s">
         <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F49" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G49" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H49" s="1">
         <v>55</v>
@@ -4363,22 +4507,22 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B50" s="7">
         <v>46255.398784722223</v>
       </c>
       <c r="C50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G50" t="s">
         <v>33</v>
@@ -4420,25 +4564,25 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B51" s="7">
         <v>46255.395833333336</v>
       </c>
       <c r="C51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D51" t="s">
         <v>26</v>
       </c>
       <c r="E51" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F51" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H51" s="1">
         <v>205</v>
@@ -4477,25 +4621,25 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B52" s="7">
         <v>46255.395833333336</v>
       </c>
       <c r="C52" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D52" t="s">
         <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H52" s="1">
         <v>205</v>
@@ -4534,25 +4678,25 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B53" s="7">
         <v>46255.614803240744</v>
       </c>
       <c r="C53" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D53" t="s">
         <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H53" s="1">
         <v>90</v>
@@ -4597,22 +4741,22 @@
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B54" s="7">
         <v>46255.715358796297</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D54" t="s">
         <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F54" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G54" t="s">
         <v>33</v>
@@ -4654,22 +4798,22 @@
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B55" s="7">
         <v>46255.715358796297</v>
       </c>
       <c r="C55" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D55" t="s">
         <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F55" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G55" t="s">
         <v>33</v>
@@ -4711,22 +4855,22 @@
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B56" s="7">
         <v>46255.705381944441</v>
       </c>
       <c r="C56" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F56" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G56" t="s">
         <v>33</v>
@@ -4768,22 +4912,22 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B57" s="7">
         <v>46255.705381944441</v>
       </c>
       <c r="C57" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D57" t="s">
         <v>26</v>
       </c>
       <c r="E57" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F57" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G57" t="s">
         <v>33</v>
@@ -4825,22 +4969,22 @@
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B58" s="7">
         <v>46280.584108796298</v>
       </c>
       <c r="C58" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D58" t="s">
         <v>26</v>
       </c>
       <c r="E58" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F58" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G58" t="s">
         <v>29</v>
@@ -4882,22 +5026,22 @@
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B59" s="7">
         <v>46258.660266203704</v>
       </c>
       <c r="C59" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D59" t="s">
         <v>26</v>
       </c>
       <c r="E59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F59" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G59" t="s">
         <v>29</v>
@@ -4939,30 +5083,30 @@
       </c>
       <c r="V59" s="7"/>
       <c r="W59" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B60" s="7">
         <v>46258.660601851851</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D60" t="s">
         <v>26</v>
       </c>
       <c r="E60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F60" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G60" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H60" s="1">
         <v>180</v>
@@ -4984,34 +5128,34 @@
         <v>3602.61</v>
       </c>
       <c r="S60" t="s">
-        <v>192</v>
+        <v>93</v>
       </c>
       <c r="T60" t="s">
         <v>44</v>
       </c>
       <c r="U60" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="V60" s="7"/>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B61" s="7">
         <v>46258.69740740741</v>
       </c>
       <c r="C61" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D61" t="s">
         <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F61" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G61" t="s">
         <v>33</v>
@@ -5047,25 +5191,25 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B62" s="7">
         <v>46258.69740740741</v>
       </c>
       <c r="C62" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D62" t="s">
         <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F62" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G62" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H62" s="1">
         <v>10</v>
@@ -5090,25 +5234,25 @@
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B63" s="7">
         <v>46259.568854166668</v>
       </c>
       <c r="C63" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D63" t="s">
         <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H63" s="1">
         <v>100</v>
@@ -5129,13 +5273,13 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B64" s="7">
         <v>46259.617465277777</v>
       </c>
       <c r="C64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D64" t="s">
         <v>26</v>
@@ -5144,10 +5288,10 @@
         <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G64" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H64" s="1">
         <v>30</v>
@@ -5186,13 +5330,13 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B65" s="7">
         <v>46259.72284722222</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D65" t="s">
         <v>26</v>
@@ -5201,10 +5345,10 @@
         <v>41</v>
       </c>
       <c r="F65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G65" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H65" s="1">
         <v>20</v>
@@ -5249,13 +5393,13 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B66" s="7">
         <v>46259.72284722222</v>
       </c>
       <c r="C66" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D66" t="s">
         <v>26</v>
@@ -5264,10 +5408,10 @@
         <v>41</v>
       </c>
       <c r="F66" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G66" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H66" s="1">
         <v>20</v>
@@ -5312,22 +5456,22 @@
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B67" s="7">
         <v>46259.724189814813</v>
       </c>
       <c r="C67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D67" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E67" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G67" t="s">
         <v>33</v>
@@ -5366,7 +5510,7 @@
         <v>3185.45</v>
       </c>
       <c r="S67" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="T67" t="s">
         <v>44</v>
@@ -5375,22 +5519,22 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B68" s="7">
         <v>46260.699502314812</v>
       </c>
       <c r="C68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D68" t="s">
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G68" t="s">
         <v>49</v>
@@ -5415,25 +5559,25 @@
         <v>2558.5</v>
       </c>
       <c r="S68" t="s">
-        <v>192</v>
+        <v>93</v>
       </c>
       <c r="T68" t="s">
         <v>44</v>
       </c>
       <c r="U68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="V68" s="7"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B69" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C69" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D69" t="s">
         <v>26</v>
@@ -5442,7 +5586,7 @@
         <v>47</v>
       </c>
       <c r="F69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G69" t="s">
         <v>29</v>
@@ -5474,17 +5618,20 @@
       <c r="R69" s="8">
         <v>14245.65</v>
       </c>
+      <c r="S69" t="s">
+        <v>43</v>
+      </c>
       <c r="V69" s="7"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B70" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C70" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D70" t="s">
         <v>26</v>
@@ -5493,10 +5640,10 @@
         <v>47</v>
       </c>
       <c r="F70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G70" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H70" s="1">
         <v>33</v>
@@ -5528,17 +5675,20 @@
       <c r="R70" s="8">
         <v>4374.9799999999996</v>
       </c>
+      <c r="S70" t="s">
+        <v>43</v>
+      </c>
       <c r="V70" s="7"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B71" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D71" t="s">
         <v>26</v>
@@ -5547,10 +5697,10 @@
         <v>47</v>
       </c>
       <c r="F71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G71" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H71" s="1">
         <v>33</v>
@@ -5582,17 +5732,20 @@
       <c r="R71" s="8">
         <v>5925.93</v>
       </c>
+      <c r="S71" t="s">
+        <v>43</v>
+      </c>
       <c r="V71" s="7"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B72" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C72" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D72" t="s">
         <v>26</v>
@@ -5601,7 +5754,7 @@
         <v>47</v>
       </c>
       <c r="F72" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G72" t="s">
         <v>29</v>
@@ -5636,17 +5789,20 @@
       <c r="R72" s="8">
         <v>4147</v>
       </c>
+      <c r="S72" t="s">
+        <v>43</v>
+      </c>
       <c r="V72" s="7"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B73" s="7">
         <v>46260.706018518518</v>
       </c>
       <c r="C73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D73" t="s">
         <v>26</v>
@@ -5655,7 +5811,7 @@
         <v>47</v>
       </c>
       <c r="F73" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G73" t="s">
         <v>29</v>
@@ -5687,17 +5843,20 @@
       <c r="R73" s="8">
         <v>4317.3</v>
       </c>
+      <c r="S73" t="s">
+        <v>43</v>
+      </c>
       <c r="V73" s="7"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B74" s="7">
         <v>46260.707881944443</v>
       </c>
       <c r="C74" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D74" t="s">
         <v>26</v>
@@ -5706,7 +5865,7 @@
         <v>47</v>
       </c>
       <c r="F74" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G74" t="s">
         <v>29</v>
@@ -5741,17 +5900,20 @@
       <c r="R74" s="8">
         <v>11527.8</v>
       </c>
+      <c r="S74" t="s">
+        <v>43</v>
+      </c>
       <c r="V74" s="7"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B75" s="7">
         <v>46260.707881944443</v>
       </c>
       <c r="C75" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D75" t="s">
         <v>26</v>
@@ -5760,7 +5922,7 @@
         <v>47</v>
       </c>
       <c r="F75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G75" t="s">
         <v>29</v>
@@ -5792,17 +5954,20 @@
       <c r="R75" s="8">
         <v>13777.2</v>
       </c>
+      <c r="S75" t="s">
+        <v>43</v>
+      </c>
       <c r="V75" s="7"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B76" s="7">
         <v>46260.707881944443</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D76" t="s">
         <v>26</v>
@@ -5811,7 +5976,7 @@
         <v>47</v>
       </c>
       <c r="F76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G76" t="s">
         <v>29</v>
@@ -5843,17 +6008,20 @@
       <c r="R76" s="8">
         <v>4372.3999999999996</v>
       </c>
+      <c r="S76" t="s">
+        <v>43</v>
+      </c>
       <c r="V76" s="7"/>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B77" s="7">
         <v>46260.707881944443</v>
       </c>
       <c r="C77" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D77" t="s">
         <v>26</v>
@@ -5862,7 +6030,7 @@
         <v>47</v>
       </c>
       <c r="F77" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G77" t="s">
         <v>29</v>
@@ -5894,17 +6062,20 @@
       <c r="R77" s="8">
         <v>11747.41</v>
       </c>
+      <c r="S77" t="s">
+        <v>43</v>
+      </c>
       <c r="V77" s="7"/>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B78" s="7">
         <v>46260.70826388889</v>
       </c>
       <c r="C78" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D78" t="s">
         <v>26</v>
@@ -5913,7 +6084,7 @@
         <v>47</v>
       </c>
       <c r="F78" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G78" t="s">
         <v>29</v>
@@ -5945,17 +6116,20 @@
       <c r="R78" s="8">
         <v>4699.08</v>
       </c>
+      <c r="S78" t="s">
+        <v>43</v>
+      </c>
       <c r="V78" s="7"/>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B79" s="7">
         <v>46260.70826388889</v>
       </c>
       <c r="C79" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D79" t="s">
         <v>26</v>
@@ -5964,7 +6138,7 @@
         <v>47</v>
       </c>
       <c r="F79" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G79" t="s">
         <v>29</v>
@@ -5996,17 +6170,20 @@
       <c r="R79" s="8">
         <v>2924.1</v>
       </c>
+      <c r="S79" t="s">
+        <v>43</v>
+      </c>
       <c r="V79" s="7"/>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B80" s="7">
         <v>46260.70826388889</v>
       </c>
       <c r="C80" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D80" t="s">
         <v>26</v>
@@ -6015,7 +6192,7 @@
         <v>47</v>
       </c>
       <c r="F80" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G80" t="s">
         <v>29</v>
@@ -6047,26 +6224,29 @@
       <c r="R80" s="8">
         <v>2924.1</v>
       </c>
+      <c r="S80" t="s">
+        <v>43</v>
+      </c>
       <c r="V80" s="7"/>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B81" s="7">
         <v>46281.721875000003</v>
       </c>
       <c r="C81" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D81" t="s">
         <v>26</v>
       </c>
       <c r="E81" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F81" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G81" t="s">
         <v>49</v>
@@ -6114,22 +6294,22 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B82" s="7">
         <v>46281.721875000003</v>
       </c>
       <c r="C82" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D82" t="s">
         <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F82" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G82" t="s">
         <v>49</v>
@@ -6177,13 +6357,13 @@
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B83" s="7">
         <v>46261.662106481483</v>
       </c>
       <c r="C83" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D83" t="s">
         <v>26</v>
@@ -6192,10 +6372,10 @@
         <v>27</v>
       </c>
       <c r="F83" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G83" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H83" s="1">
         <v>10</v>
@@ -6234,13 +6414,13 @@
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B84" s="7">
         <v>46261.662106481483</v>
       </c>
       <c r="C84" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D84" t="s">
         <v>26</v>
@@ -6249,7 +6429,7 @@
         <v>27</v>
       </c>
       <c r="F84" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G84" t="s">
         <v>38</v>
@@ -6291,25 +6471,25 @@
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B85" s="7">
         <v>46280.713750000003</v>
       </c>
       <c r="C85" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D85" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E85" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F85" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H85" s="1">
         <v>1000</v>
@@ -6334,22 +6514,22 @@
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B86" s="7">
         <v>46266.589988425927</v>
       </c>
       <c r="C86" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E86" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F86" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G86" t="s">
         <v>33</v>
@@ -6374,7 +6554,7 @@
         <v>3803.52</v>
       </c>
       <c r="S86" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="T86" t="s">
         <v>44</v>
@@ -6383,25 +6563,25 @@
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B87" s="7">
         <v>46266.556886574072</v>
       </c>
       <c r="C87" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D87" t="s">
         <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F87" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G87" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H87" s="1">
         <v>150</v>
@@ -6428,25 +6608,25 @@
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B88" s="7">
         <v>46266.556886574072</v>
       </c>
       <c r="C88" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D88" t="s">
         <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
+        <v>253</v>
+      </c>
+      <c r="G88" t="s">
         <v>252</v>
-      </c>
-      <c r="G88" t="s">
-        <v>251</v>
       </c>
       <c r="H88" s="1">
         <v>60</v>
@@ -6473,25 +6653,25 @@
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B89" s="7">
         <v>46262.725381944445</v>
       </c>
       <c r="C89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D89" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E89" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F89" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G89" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H89" s="1">
         <v>150</v>
@@ -6530,22 +6710,22 @@
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B90" s="7">
         <v>46265.689513888887</v>
       </c>
       <c r="C90" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E90" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F90" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G90" t="s">
         <v>33</v>
@@ -6578,34 +6758,34 @@
         <v>9597.1200000000008</v>
       </c>
       <c r="S90" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="T90" t="s">
         <v>44</v>
       </c>
       <c r="U90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="V90" s="7"/>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B91" s="7">
         <v>46265.689513888887</v>
       </c>
       <c r="C91" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E91" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F91" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G91" t="s">
         <v>33</v>
@@ -6644,37 +6824,37 @@
         <v>3381.33</v>
       </c>
       <c r="S91" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="T91" t="s">
         <v>44</v>
       </c>
       <c r="U91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="V91" s="7"/>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B92" s="7">
         <v>46279.438460648147</v>
       </c>
       <c r="C92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D92" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E92" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F92" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H92" s="1">
         <v>25</v>
@@ -6719,25 +6899,25 @@
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B93" s="7">
         <v>46267.733101851853</v>
       </c>
       <c r="C93" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D93" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E93" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G93" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H93" s="1">
         <v>20</v>
@@ -6776,25 +6956,25 @@
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B94" s="7">
         <v>46267.733101851853</v>
       </c>
       <c r="C94" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E94" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F94" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G94" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H94" s="1">
         <v>10</v>
@@ -6833,25 +7013,25 @@
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B95" s="7">
         <v>46268.44902777778</v>
       </c>
       <c r="C95" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D95" t="s">
         <v>26</v>
       </c>
       <c r="E95" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F95" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G95" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H95" s="1">
         <v>4</v>
@@ -6883,25 +7063,25 @@
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B96" s="7">
         <v>46268.44902777778</v>
       </c>
       <c r="C96" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D96" t="s">
         <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F96" t="s">
+        <v>278</v>
+      </c>
+      <c r="G96" t="s">
         <v>277</v>
-      </c>
-      <c r="G96" t="s">
-        <v>276</v>
       </c>
       <c r="H96" s="1">
         <v>4</v>
@@ -6933,25 +7113,25 @@
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B97" s="7">
         <v>46268.44902777778</v>
       </c>
       <c r="C97" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D97" t="s">
         <v>26</v>
       </c>
       <c r="E97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F97" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G97" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H97" s="1">
         <v>4</v>
@@ -6981,25 +7161,25 @@
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B98" s="7">
         <v>46280.572372685187</v>
       </c>
       <c r="C98" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D98" t="s">
         <v>26</v>
       </c>
       <c r="E98" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F98" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G98" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H98" s="1">
         <v>100</v>
@@ -7035,7 +7215,7 @@
         <v>4237.3</v>
       </c>
       <c r="S98" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="T98" t="s">
         <v>44</v>
@@ -7044,22 +7224,22 @@
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B99" s="7">
         <v>46273.645821759259</v>
       </c>
       <c r="C99" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D99" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F99" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G99" t="s">
         <v>33</v>
@@ -7098,7 +7278,7 @@
         <v>1483</v>
       </c>
       <c r="S99" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="T99" t="s">
         <v>44</v>
@@ -7107,22 +7287,22 @@
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B100" s="7">
         <v>46273.645821759259</v>
       </c>
       <c r="C100" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D100" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E100" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F100" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G100" t="s">
         <v>33</v>
@@ -7161,7 +7341,7 @@
         <v>2542</v>
       </c>
       <c r="S100" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="T100" t="s">
         <v>44</v>
@@ -7170,13 +7350,13 @@
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B101" s="7">
         <v>46280.583483796298</v>
       </c>
       <c r="C101" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D101" t="s">
         <v>26</v>
@@ -7185,10 +7365,10 @@
         <v>47</v>
       </c>
       <c r="F101" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G101" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H101" s="1">
         <v>20</v>
@@ -7227,22 +7407,22 @@
     </row>
     <row r="102" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B102" s="7">
         <v>46275.466377314813</v>
       </c>
       <c r="C102" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D102" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E102" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F102" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G102" t="s">
         <v>33</v>
@@ -7284,22 +7464,22 @@
     </row>
     <row r="103" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B103" s="7">
         <v>46279.439363425925</v>
       </c>
       <c r="C103" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D103" t="s">
         <v>26</v>
       </c>
       <c r="E103" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F103" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G103" t="s">
         <v>33</v>
@@ -7341,25 +7521,25 @@
     </row>
     <row r="104" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B104" s="7">
         <v>46276.397337962961</v>
       </c>
       <c r="C104" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D104" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
       </c>
       <c r="F104" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G104" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H104" s="1">
         <v>60</v>
@@ -7398,22 +7578,22 @@
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B105" s="7">
         <v>46279.607939814814</v>
       </c>
       <c r="C105" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D105" t="s">
         <v>26</v>
       </c>
       <c r="E105" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F105" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G105" t="s">
         <v>33</v>
@@ -7455,25 +7635,25 @@
     </row>
     <row r="106" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B106" s="7">
         <v>46279.619386574072</v>
       </c>
       <c r="C106" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D106" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
       </c>
       <c r="F106" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G106" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H106" s="1">
         <v>50</v>
@@ -7512,22 +7692,22 @@
     </row>
     <row r="107" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B107" s="7">
         <v>46287.559652777774</v>
       </c>
       <c r="C107" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D107" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E107" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F107" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G107" t="s">
         <v>49</v>
@@ -7569,22 +7749,22 @@
     </row>
     <row r="108" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B108" s="7">
         <v>46287.559652777774</v>
       </c>
       <c r="C108" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D108" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E108" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F108" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G108" t="s">
         <v>49</v>
@@ -7626,22 +7806,22 @@
     </row>
     <row r="109" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B109" s="7">
         <v>46287.559652777774</v>
       </c>
       <c r="C109" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D109" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E109" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F109" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G109" t="s">
         <v>29</v>
@@ -7683,22 +7863,22 @@
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B110" s="7">
         <v>46287.559652777774</v>
       </c>
       <c r="C110" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D110" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E110" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F110" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G110" t="s">
         <v>33</v>
@@ -7740,22 +7920,22 @@
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B111" s="7">
         <v>46281.721805555557</v>
       </c>
       <c r="C111" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D111" t="s">
         <v>26</v>
       </c>
       <c r="E111" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F111" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G111" t="s">
         <v>49</v>
@@ -7797,22 +7977,22 @@
     </row>
     <row r="112" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B112" s="7">
         <v>46281.721805555557</v>
       </c>
       <c r="C112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D112" t="s">
         <v>26</v>
       </c>
       <c r="E112" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F112" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G112" t="s">
         <v>49</v>
@@ -7854,22 +8034,22 @@
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B113" s="7">
         <v>46281.721805555557</v>
       </c>
       <c r="C113" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D113" t="s">
         <v>26</v>
       </c>
       <c r="E113" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F113" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G113" t="s">
         <v>29</v>
@@ -7911,25 +8091,25 @@
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B114" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C114" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D114" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
       </c>
       <c r="F114" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G114" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H114" s="1">
         <v>15</v>
@@ -7968,25 +8148,25 @@
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B115" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C115" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D115" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
       </c>
       <c r="F115" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G115" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H115" s="1">
         <v>12</v>
@@ -8025,25 +8205,25 @@
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B116" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C116" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D116" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
       </c>
       <c r="F116" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G116" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H116" s="1">
         <v>30</v>
@@ -8082,22 +8262,22 @@
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B117" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C117" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D117" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
       </c>
       <c r="F117" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G117" t="s">
         <v>29</v>
@@ -8139,25 +8319,25 @@
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B118" s="7">
         <v>46279.645798611113</v>
       </c>
       <c r="C118" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D118" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
       </c>
       <c r="F118" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G118" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H118" s="1">
         <v>60</v>
@@ -8196,22 +8376,22 @@
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B119" s="7">
         <v>46279.700057870374</v>
       </c>
       <c r="C119" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D119" t="s">
         <v>26</v>
       </c>
       <c r="E119" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F119" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G119" t="s">
         <v>33</v>
@@ -8253,22 +8433,22 @@
     </row>
     <row r="120" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B120" s="7">
         <v>46282.705983796295</v>
       </c>
       <c r="C120" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
       </c>
       <c r="E120" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F120" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G120" t="s">
         <v>29</v>
@@ -8310,13 +8490,13 @@
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B121" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C121" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D121" t="s">
         <v>26</v>
@@ -8325,7 +8505,7 @@
         <v>27</v>
       </c>
       <c r="F121" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G121" t="s">
         <v>29</v>
@@ -8367,13 +8547,13 @@
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B122" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C122" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D122" t="s">
         <v>26</v>
@@ -8382,7 +8562,7 @@
         <v>27</v>
       </c>
       <c r="F122" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G122" t="s">
         <v>29</v>
@@ -8424,13 +8604,13 @@
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B123" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C123" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D123" t="s">
         <v>26</v>
@@ -8439,7 +8619,7 @@
         <v>27</v>
       </c>
       <c r="F123" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G123" t="s">
         <v>29</v>
@@ -8481,13 +8661,13 @@
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B124" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C124" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D124" t="s">
         <v>26</v>
@@ -8496,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="F124" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G124" t="s">
         <v>29</v>
@@ -8538,13 +8718,13 @@
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B125" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C125" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D125" t="s">
         <v>26</v>
@@ -8553,7 +8733,7 @@
         <v>27</v>
       </c>
       <c r="F125" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G125" t="s">
         <v>29</v>
@@ -8595,13 +8775,13 @@
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B126" s="7">
         <v>46287.540856481479</v>
       </c>
       <c r="C126" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D126" t="s">
         <v>26</v>
@@ -8610,10 +8790,10 @@
         <v>47</v>
       </c>
       <c r="F126" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G126" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H126" s="1">
         <v>300</v>
@@ -8652,13 +8832,13 @@
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B127" s="7">
         <v>46287.540856481479</v>
       </c>
       <c r="C127" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D127" t="s">
         <v>26</v>
@@ -8667,10 +8847,10 @@
         <v>47</v>
       </c>
       <c r="F127" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G127" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H127" s="1">
         <v>300</v>
@@ -8709,25 +8889,25 @@
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B128" s="7">
         <v>46287.66646990741</v>
       </c>
       <c r="C128" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D128" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E128" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F128" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G128" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H128" s="1">
         <v>250</v>
@@ -8766,22 +8946,22 @@
     </row>
     <row r="129" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B129" s="7">
         <v>46287.66646990741</v>
       </c>
       <c r="C129" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D129" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E129" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F129" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G129" t="s">
         <v>33</v>
@@ -8823,25 +9003,25 @@
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B130" s="7">
         <v>46287.66646990741</v>
       </c>
       <c r="C130" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D130" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E130" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F130" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G130" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H130" s="1">
         <v>5000</v>
@@ -8880,22 +9060,22 @@
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B131" s="7">
         <v>46287.649074074077</v>
       </c>
       <c r="C131" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D131" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E131" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F131" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G131" t="s">
         <v>33</v>
@@ -8937,25 +9117,25 @@
     </row>
     <row r="132" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B132" s="7">
         <v>46287.644872685189</v>
       </c>
       <c r="C132" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D132" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E132" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F132" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G132" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H132" s="1">
         <v>100</v>
@@ -8994,22 +9174,22 @@
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B133" s="7">
         <v>46288.702326388891</v>
       </c>
       <c r="C133" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D133" t="s">
         <v>26</v>
       </c>
       <c r="E133" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F133" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G133" t="s">
         <v>33</v>
@@ -9051,22 +9231,22 @@
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B134" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C134" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D134" t="s">
         <v>26</v>
       </c>
       <c r="E134" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F134" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G134" t="s">
         <v>33</v>
@@ -9108,22 +9288,22 @@
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B135" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C135" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D135" t="s">
         <v>26</v>
       </c>
       <c r="E135" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F135" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G135" t="s">
         <v>33</v>
@@ -9165,25 +9345,25 @@
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B136" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C136" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D136" t="s">
         <v>26</v>
       </c>
       <c r="E136" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F136" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G136" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H136" s="1">
         <v>295</v>
@@ -9222,25 +9402,25 @@
     </row>
     <row r="137" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B137" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C137" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D137" t="s">
         <v>26</v>
       </c>
       <c r="E137" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F137" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G137" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H137" s="1">
         <v>480</v>
@@ -9273,13 +9453,13 @@
     </row>
     <row r="138" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B138" s="7">
         <v>46288.70853009259</v>
       </c>
       <c r="C138" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D138" t="s">
         <v>26</v>
@@ -9288,10 +9468,10 @@
         <v>41</v>
       </c>
       <c r="F138" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G138" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H138" s="1">
         <v>300</v>
@@ -9330,22 +9510,22 @@
     </row>
     <row r="139" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B139" s="7">
         <v>46289.572893518518</v>
       </c>
       <c r="C139" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D139" t="s">
         <v>26</v>
       </c>
       <c r="E139" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F139" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G139" t="s">
         <v>29</v>
@@ -9387,22 +9567,22 @@
     </row>
     <row r="140" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B140" s="7">
         <v>46289.569641203707</v>
       </c>
       <c r="C140" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D140" t="s">
         <v>26</v>
       </c>
       <c r="E140" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F140" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G140" t="s">
         <v>33</v>
@@ -9444,25 +9624,25 @@
     </row>
     <row r="141" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B141" s="7">
         <v>46289.567453703705</v>
       </c>
       <c r="C141" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D141" t="s">
         <v>26</v>
       </c>
       <c r="E141" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F141" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G141" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H141" s="1">
         <v>5</v>
@@ -9501,22 +9681,22 @@
     </row>
     <row r="142" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B142" s="7">
         <v>46289.571481481478</v>
       </c>
       <c r="C142" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D142" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E142" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F142" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G142" t="s">
         <v>29</v>
@@ -9558,25 +9738,25 @@
     </row>
     <row r="143" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B143" s="7">
         <v>46289.718541666669</v>
       </c>
       <c r="C143" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D143" t="s">
         <v>26</v>
       </c>
       <c r="E143" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F143" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G143" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H143" s="1">
         <v>135</v>
@@ -9615,25 +9795,25 @@
     </row>
     <row r="144" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B144" s="7">
         <v>46289.718541666669</v>
       </c>
       <c r="C144" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D144" t="s">
         <v>26</v>
       </c>
       <c r="E144" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F144" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G144" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H144" s="1">
         <v>500</v>
@@ -9672,22 +9852,22 @@
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B145" s="7">
         <v>46290.663263888891</v>
       </c>
       <c r="C145" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D145" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E145" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F145" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G145" t="s">
         <v>33</v>
@@ -9729,25 +9909,25 @@
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B146" s="7">
         <v>46290.663263888891</v>
       </c>
       <c r="C146" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D146" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E146" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F146" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G146" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H146" s="1">
         <v>65</v>
@@ -9786,22 +9966,22 @@
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B147" s="7">
         <v>46295.710763888892</v>
       </c>
       <c r="C147" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D147" t="s">
         <v>26</v>
       </c>
       <c r="E147" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F147" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G147" t="s">
         <v>33</v>
@@ -9843,22 +10023,22 @@
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B148" s="7">
         <v>46294.695925925924</v>
       </c>
       <c r="C148" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D148" t="s">
         <v>26</v>
       </c>
       <c r="E148" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F148" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H148" s="1">
         <v>72</v>
@@ -9897,25 +10077,25 @@
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B149" s="7">
         <v>46295.662303240744</v>
       </c>
       <c r="C149" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D149" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E149" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F149" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G149" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H149" s="1">
         <v>60</v>
@@ -9954,22 +10134,22 @@
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B150" s="7">
         <v>46295.662303240744</v>
       </c>
       <c r="C150" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D150" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E150" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F150" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G150" t="s">
         <v>33</v>
@@ -10011,25 +10191,25 @@
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B151" s="7">
         <v>46295.662303240744</v>
       </c>
       <c r="C151" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E151" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F151" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G151" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H151" s="1">
         <v>30</v>
@@ -10068,22 +10248,22 @@
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B152" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C152" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D152" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E152" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F152" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G152" t="s">
         <v>33</v>
@@ -10125,25 +10305,25 @@
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B153" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C153" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D153" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E153" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F153" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G153" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H153" s="1">
         <v>50</v>
@@ -10182,22 +10362,22 @@
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B154" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C154" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D154" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E154" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F154" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G154" t="s">
         <v>33</v>
@@ -10239,22 +10419,22 @@
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B155" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C155" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D155" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E155" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F155" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G155" t="s">
         <v>33</v>
@@ -10296,25 +10476,25 @@
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B156" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C156" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D156" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E156" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F156" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G156" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H156" s="1">
         <v>50</v>
@@ -10353,22 +10533,22 @@
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B157" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C157" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D157" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E157" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F157" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G157" t="s">
         <v>33</v>
@@ -10410,25 +10590,25 @@
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B158" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C158" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D158" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E158" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F158" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G158" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H158" s="1">
         <v>50</v>
@@ -10467,25 +10647,25 @@
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B159" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C159" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D159" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E159" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F159" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G159" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H159" s="1">
         <v>75</v>
@@ -10524,25 +10704,25 @@
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B160" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C160" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D160" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E160" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F160" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G160" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H160" s="1">
         <v>130</v>
@@ -10581,22 +10761,22 @@
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B161" s="7">
         <v>46295.67895833333</v>
       </c>
       <c r="C161" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D161" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E161" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F161" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G161" t="s">
         <v>33</v>
@@ -10638,25 +10818,25 @@
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B162" s="7">
         <v>46295.67895833333</v>
       </c>
       <c r="C162" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D162" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E162" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F162" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G162" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H162" s="1">
         <v>35</v>
@@ -10695,22 +10875,22 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B163" s="7">
         <v>46295.67895833333</v>
       </c>
       <c r="C163" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D163" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E163" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F163" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G163" t="s">
         <v>33</v>
@@ -10752,25 +10932,25 @@
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B164" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C164" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D164" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E164" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F164" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G164" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H164" s="1">
         <v>100</v>
@@ -10809,25 +10989,25 @@
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B165" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C165" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E165" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F165" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G165" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H165" s="1">
         <v>50</v>
@@ -10866,25 +11046,25 @@
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B166" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C166" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D166" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E166" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F166" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G166" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H166" s="1">
         <v>50</v>
@@ -10923,25 +11103,25 @@
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B167" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C167" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D167" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E167" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F167" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G167" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H167" s="1">
         <v>50</v>
@@ -10980,22 +11160,22 @@
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B168" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C168" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D168" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E168" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F168" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G168" t="s">
         <v>29</v>
@@ -11037,25 +11217,25 @@
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B169" s="7">
         <v>46296.652222222219</v>
       </c>
       <c r="C169" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D169" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E169" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F169" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G169" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H169" s="1">
         <v>1000</v>
@@ -11093,94 +11273,765 @@
       <c r="V169" s="7"/>
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B170" s="7"/>
+      <c r="A170" t="s">
+        <v>413</v>
+      </c>
+      <c r="B170" s="7">
+        <v>46297.609618055554</v>
+      </c>
+      <c r="C170" t="s">
+        <v>208</v>
+      </c>
+      <c r="D170" t="s">
+        <v>26</v>
+      </c>
+      <c r="E170" t="s">
+        <v>41</v>
+      </c>
+      <c r="F170" t="s">
+        <v>414</v>
+      </c>
+      <c r="G170" t="s">
+        <v>33</v>
+      </c>
+      <c r="H170" s="1">
+        <v>3720</v>
+      </c>
+      <c r="I170" s="8">
+        <v>11.74</v>
+      </c>
+      <c r="J170" s="8">
+        <v>43672.800000000003</v>
+      </c>
+      <c r="Q170" s="8">
+        <v>0</v>
+      </c>
+      <c r="R170" s="8">
+        <v>43672.800000000003</v>
+      </c>
       <c r="V170" s="7"/>
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B171" s="7"/>
+      <c r="A171" t="s">
+        <v>415</v>
+      </c>
+      <c r="B171" s="7">
+        <v>46297.679155092592</v>
+      </c>
+      <c r="C171" t="s">
+        <v>416</v>
+      </c>
+      <c r="D171" t="s">
+        <v>57</v>
+      </c>
+      <c r="E171" t="s">
+        <v>417</v>
+      </c>
+      <c r="F171" t="s">
+        <v>418</v>
+      </c>
+      <c r="G171" t="s">
+        <v>70</v>
+      </c>
+      <c r="H171" s="1">
+        <v>720</v>
+      </c>
+      <c r="I171" s="8">
+        <v>10.57</v>
+      </c>
+      <c r="J171" s="8">
+        <v>7610.4</v>
+      </c>
+      <c r="K171" s="1">
+        <v>0</v>
+      </c>
+      <c r="L171" s="8">
+        <v>0</v>
+      </c>
+      <c r="M171" s="8">
+        <v>0</v>
+      </c>
+      <c r="N171" s="1">
+        <v>0</v>
+      </c>
+      <c r="O171" s="8">
+        <v>0</v>
+      </c>
+      <c r="P171" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="8">
+        <v>0</v>
+      </c>
+      <c r="R171" s="8">
+        <v>7610.4</v>
+      </c>
       <c r="V171" s="7"/>
     </row>
     <row r="172" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B172" s="7"/>
+      <c r="A172" t="s">
+        <v>415</v>
+      </c>
+      <c r="B172" s="7">
+        <v>46297.679155092592</v>
+      </c>
+      <c r="C172" t="s">
+        <v>416</v>
+      </c>
+      <c r="D172" t="s">
+        <v>57</v>
+      </c>
+      <c r="E172" t="s">
+        <v>417</v>
+      </c>
+      <c r="F172" t="s">
+        <v>419</v>
+      </c>
+      <c r="G172" t="s">
+        <v>64</v>
+      </c>
+      <c r="H172" s="1">
+        <v>200</v>
+      </c>
+      <c r="I172" s="8">
+        <v>10.34</v>
+      </c>
+      <c r="J172" s="8">
+        <v>2068</v>
+      </c>
+      <c r="K172" s="1">
+        <v>0</v>
+      </c>
+      <c r="L172" s="8">
+        <v>0</v>
+      </c>
+      <c r="M172" s="8">
+        <v>0</v>
+      </c>
+      <c r="N172" s="1">
+        <v>0</v>
+      </c>
+      <c r="O172" s="8">
+        <v>0</v>
+      </c>
+      <c r="P172" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="8">
+        <v>0</v>
+      </c>
+      <c r="R172" s="8">
+        <v>2068</v>
+      </c>
       <c r="V172" s="7"/>
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B173" s="7"/>
+      <c r="A173" t="s">
+        <v>415</v>
+      </c>
+      <c r="B173" s="7">
+        <v>46297.679155092592</v>
+      </c>
+      <c r="C173" t="s">
+        <v>416</v>
+      </c>
+      <c r="D173" t="s">
+        <v>57</v>
+      </c>
+      <c r="E173" t="s">
+        <v>417</v>
+      </c>
+      <c r="F173" t="s">
+        <v>420</v>
+      </c>
+      <c r="G173" t="s">
+        <v>70</v>
+      </c>
+      <c r="H173" s="1">
+        <v>200</v>
+      </c>
+      <c r="I173" s="8">
+        <v>21.64</v>
+      </c>
+      <c r="J173" s="8">
+        <v>4328</v>
+      </c>
+      <c r="K173" s="1">
+        <v>0</v>
+      </c>
+      <c r="L173" s="8">
+        <v>0</v>
+      </c>
+      <c r="M173" s="8">
+        <v>0</v>
+      </c>
+      <c r="N173" s="1">
+        <v>0</v>
+      </c>
+      <c r="O173" s="8">
+        <v>0</v>
+      </c>
+      <c r="P173" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="8">
+        <v>0</v>
+      </c>
+      <c r="R173" s="8">
+        <v>4328</v>
+      </c>
       <c r="V173" s="7"/>
     </row>
     <row r="174" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B174" s="7"/>
+      <c r="A174" t="s">
+        <v>421</v>
+      </c>
+      <c r="B174" s="7">
+        <v>46297.730497685188</v>
+      </c>
+      <c r="C174" t="s">
+        <v>422</v>
+      </c>
+      <c r="D174" t="s">
+        <v>423</v>
+      </c>
+      <c r="E174" t="s">
+        <v>424</v>
+      </c>
+      <c r="F174" t="s">
+        <v>425</v>
+      </c>
+      <c r="G174" t="s">
+        <v>49</v>
+      </c>
+      <c r="H174" s="1">
+        <v>500</v>
+      </c>
+      <c r="I174" s="8">
+        <v>38.75</v>
+      </c>
+      <c r="J174" s="8">
+        <v>19375</v>
+      </c>
+      <c r="K174" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L174" s="8">
+        <v>30.78</v>
+      </c>
+      <c r="M174" s="8">
+        <v>30780</v>
+      </c>
+      <c r="N174" s="1">
+        <v>0</v>
+      </c>
+      <c r="O174" s="8">
+        <v>0</v>
+      </c>
+      <c r="P174" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="8">
+        <v>0</v>
+      </c>
+      <c r="R174" s="8">
+        <v>25077.5</v>
+      </c>
       <c r="V174" s="7"/>
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B175" s="7"/>
+      <c r="A175" t="s">
+        <v>426</v>
+      </c>
+      <c r="B175" s="7">
+        <v>46300.351354166669</v>
+      </c>
+      <c r="C175" t="s">
+        <v>427</v>
+      </c>
+      <c r="D175" t="s">
+        <v>26</v>
+      </c>
+      <c r="E175" t="s">
+        <v>62</v>
+      </c>
+      <c r="F175" t="s">
+        <v>428</v>
+      </c>
+      <c r="G175" t="s">
+        <v>29</v>
+      </c>
+      <c r="H175" s="1">
+        <v>100</v>
+      </c>
+      <c r="I175" s="8">
+        <v>23.47</v>
+      </c>
+      <c r="J175" s="8">
+        <v>2347</v>
+      </c>
+      <c r="K175" s="1">
+        <v>150</v>
+      </c>
+      <c r="L175" s="8">
+        <v>21.18</v>
+      </c>
+      <c r="M175" s="8">
+        <v>3177</v>
+      </c>
+      <c r="N175" s="1">
+        <v>200</v>
+      </c>
+      <c r="O175" s="8">
+        <v>20.43</v>
+      </c>
+      <c r="P175" s="8">
+        <v>4086</v>
+      </c>
+      <c r="Q175" s="8">
+        <v>0</v>
+      </c>
+      <c r="R175" s="8">
+        <v>3203.33</v>
+      </c>
       <c r="V175" s="7"/>
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B176" s="7"/>
+      <c r="A176" t="s">
+        <v>429</v>
+      </c>
+      <c r="B176" s="7">
+        <v>46300.35019675926</v>
+      </c>
+      <c r="C176" t="s">
+        <v>430</v>
+      </c>
+      <c r="D176" t="s">
+        <v>26</v>
+      </c>
+      <c r="E176" t="s">
+        <v>62</v>
+      </c>
+      <c r="F176" t="s">
+        <v>431</v>
+      </c>
+      <c r="G176" t="s">
+        <v>101</v>
+      </c>
+      <c r="H176" s="1">
+        <v>160</v>
+      </c>
+      <c r="I176" s="8">
+        <v>18.5</v>
+      </c>
+      <c r="J176" s="8">
+        <v>2960</v>
+      </c>
+      <c r="K176" s="1">
+        <v>215</v>
+      </c>
+      <c r="L176" s="8">
+        <v>15.81</v>
+      </c>
+      <c r="M176" s="8">
+        <v>3399.15</v>
+      </c>
+      <c r="N176" s="1">
+        <v>290</v>
+      </c>
+      <c r="O176" s="8">
+        <v>14.06</v>
+      </c>
+      <c r="P176" s="8">
+        <v>4077.4</v>
+      </c>
+      <c r="Q176" s="8">
+        <v>0</v>
+      </c>
+      <c r="R176" s="8">
+        <v>3478.85</v>
+      </c>
       <c r="V176" s="7"/>
     </row>
-    <row r="177" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B177" s="7"/>
+    <row r="177" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>432</v>
+      </c>
+      <c r="B177" s="7">
+        <v>46300.356377314813</v>
+      </c>
+      <c r="C177" t="s">
+        <v>433</v>
+      </c>
+      <c r="D177" t="s">
+        <v>247</v>
+      </c>
+      <c r="E177" t="s">
+        <v>292</v>
+      </c>
+      <c r="F177" t="s">
+        <v>434</v>
+      </c>
+      <c r="G177" t="s">
+        <v>33</v>
+      </c>
+      <c r="H177" s="1">
+        <v>115</v>
+      </c>
+      <c r="I177" s="8">
+        <v>22.09</v>
+      </c>
+      <c r="J177" s="8">
+        <v>2540.35</v>
+      </c>
+      <c r="K177" s="1">
+        <v>155</v>
+      </c>
+      <c r="L177" s="8">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="M177" s="8">
+        <v>3162</v>
+      </c>
+      <c r="N177" s="1">
+        <v>210</v>
+      </c>
+      <c r="O177" s="8">
+        <v>18.23</v>
+      </c>
+      <c r="P177" s="8">
+        <v>3828.3</v>
+      </c>
+      <c r="Q177" s="8">
+        <v>0</v>
+      </c>
+      <c r="R177" s="8">
+        <v>3176.88</v>
+      </c>
       <c r="V177" s="7"/>
     </row>
-    <row r="178" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B178" s="7"/>
+    <row r="178" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>435</v>
+      </c>
+      <c r="B178" s="7">
+        <v>46300.359131944446</v>
+      </c>
+      <c r="C178" t="s">
+        <v>436</v>
+      </c>
+      <c r="D178" t="s">
+        <v>124</v>
+      </c>
+      <c r="E178" t="s">
+        <v>176</v>
+      </c>
+      <c r="F178" t="s">
+        <v>437</v>
+      </c>
+      <c r="G178" t="s">
+        <v>33</v>
+      </c>
+      <c r="H178" s="1">
+        <v>50</v>
+      </c>
+      <c r="I178" s="8">
+        <v>51.61</v>
+      </c>
+      <c r="J178" s="8">
+        <v>2580.5</v>
+      </c>
+      <c r="K178" s="1">
+        <v>70</v>
+      </c>
+      <c r="L178" s="8">
+        <v>47.16</v>
+      </c>
+      <c r="M178" s="8">
+        <v>3301.2</v>
+      </c>
+      <c r="N178" s="1">
+        <v>95</v>
+      </c>
+      <c r="O178" s="8">
+        <v>43.12</v>
+      </c>
+      <c r="P178" s="8">
+        <v>4096.3999999999996</v>
+      </c>
+      <c r="Q178" s="8">
+        <v>0</v>
+      </c>
+      <c r="R178" s="8">
+        <v>3326.03</v>
+      </c>
       <c r="V178" s="7"/>
     </row>
-    <row r="179" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B179" s="7"/>
+    <row r="179" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>438</v>
+      </c>
+      <c r="B179" s="7">
+        <v>46300.384212962963</v>
+      </c>
+      <c r="C179" t="s">
+        <v>439</v>
+      </c>
+      <c r="D179" t="s">
+        <v>26</v>
+      </c>
+      <c r="E179" t="s">
+        <v>119</v>
+      </c>
+      <c r="F179" t="s">
+        <v>440</v>
+      </c>
+      <c r="G179" t="s">
+        <v>441</v>
+      </c>
+      <c r="H179" s="1">
+        <v>500</v>
+      </c>
+      <c r="I179" s="8">
+        <v>44.75</v>
+      </c>
+      <c r="J179" s="8">
+        <v>22375</v>
+      </c>
+      <c r="K179" s="1">
+        <v>0</v>
+      </c>
+      <c r="L179" s="8">
+        <v>0</v>
+      </c>
+      <c r="M179" s="8">
+        <v>0</v>
+      </c>
+      <c r="N179" s="1">
+        <v>0</v>
+      </c>
+      <c r="O179" s="8">
+        <v>0</v>
+      </c>
+      <c r="P179" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="8">
+        <v>0</v>
+      </c>
+      <c r="R179" s="8">
+        <v>22375</v>
+      </c>
       <c r="V179" s="7"/>
     </row>
-    <row r="180" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B180" s="7"/>
+    <row r="180" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>442</v>
+      </c>
+      <c r="B180" s="7">
+        <v>46300.362326388888</v>
+      </c>
+      <c r="C180" t="s">
+        <v>443</v>
+      </c>
+      <c r="D180" t="s">
+        <v>260</v>
+      </c>
+      <c r="E180" t="s">
+        <v>444</v>
+      </c>
+      <c r="F180" t="s">
+        <v>445</v>
+      </c>
+      <c r="G180" t="s">
+        <v>33</v>
+      </c>
+      <c r="H180" s="1">
+        <v>20</v>
+      </c>
+      <c r="I180" s="8">
+        <v>142.63999999999999</v>
+      </c>
+      <c r="J180" s="8">
+        <v>2852.8</v>
+      </c>
+      <c r="K180" s="1">
+        <v>30</v>
+      </c>
+      <c r="L180" s="8">
+        <v>117.42</v>
+      </c>
+      <c r="M180" s="8">
+        <v>3522.6</v>
+      </c>
+      <c r="N180" s="1">
+        <v>40</v>
+      </c>
+      <c r="O180" s="8">
+        <v>81.96</v>
+      </c>
+      <c r="P180" s="8">
+        <v>3278.4</v>
+      </c>
+      <c r="Q180" s="8">
+        <v>0</v>
+      </c>
+      <c r="R180" s="8">
+        <v>3217.93</v>
+      </c>
       <c r="V180" s="7"/>
     </row>
-    <row r="181" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B181" s="7"/>
+    <row r="181" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>442</v>
+      </c>
+      <c r="B181" s="7">
+        <v>46300.362326388888</v>
+      </c>
+      <c r="C181" t="s">
+        <v>443</v>
+      </c>
+      <c r="D181" t="s">
+        <v>260</v>
+      </c>
+      <c r="E181" t="s">
+        <v>444</v>
+      </c>
+      <c r="F181" t="s">
+        <v>446</v>
+      </c>
+      <c r="G181" t="s">
+        <v>33</v>
+      </c>
+      <c r="H181" s="1">
+        <v>15</v>
+      </c>
+      <c r="I181" s="8">
+        <v>224.18</v>
+      </c>
+      <c r="J181" s="8">
+        <v>3362.7</v>
+      </c>
+      <c r="K181" s="1">
+        <v>20</v>
+      </c>
+      <c r="L181" s="8">
+        <v>196.21</v>
+      </c>
+      <c r="M181" s="8">
+        <v>3924.2</v>
+      </c>
+      <c r="N181" s="1">
+        <v>30</v>
+      </c>
+      <c r="O181" s="8">
+        <v>167.13</v>
+      </c>
+      <c r="P181" s="8">
+        <v>5013.8999999999996</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>0</v>
+      </c>
+      <c r="R181" s="8">
+        <v>4100.2700000000004</v>
+      </c>
       <c r="V181" s="7"/>
     </row>
-    <row r="182" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B182" s="7"/>
+    <row r="182" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>447</v>
+      </c>
+      <c r="B182" s="7">
+        <v>46300.386967592596</v>
+      </c>
+      <c r="C182" t="s">
+        <v>448</v>
+      </c>
+      <c r="D182" t="s">
+        <v>26</v>
+      </c>
+      <c r="E182" t="s">
+        <v>449</v>
+      </c>
+      <c r="F182" t="s">
+        <v>450</v>
+      </c>
+      <c r="G182" t="s">
+        <v>33</v>
+      </c>
+      <c r="H182" s="1">
+        <v>20</v>
+      </c>
+      <c r="I182" s="8">
+        <v>157.75</v>
+      </c>
+      <c r="J182" s="8">
+        <v>3155</v>
+      </c>
+      <c r="K182" s="1">
+        <v>30</v>
+      </c>
+      <c r="L182" s="8">
+        <v>142.51</v>
+      </c>
+      <c r="M182" s="8">
+        <v>4275.3</v>
+      </c>
+      <c r="N182" s="1">
+        <v>40</v>
+      </c>
+      <c r="O182" s="8">
+        <v>131.03</v>
+      </c>
+      <c r="P182" s="8">
+        <v>5241.2</v>
+      </c>
+      <c r="Q182" s="8">
+        <v>0</v>
+      </c>
+      <c r="R182" s="8">
+        <v>4223.83</v>
+      </c>
       <c r="V182" s="7"/>
     </row>
-    <row r="183" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B183" s="7"/>
       <c r="V183" s="7"/>
     </row>
-    <row r="184" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B184" s="7"/>
       <c r="V184" s="7"/>
     </row>
-    <row r="185" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B185" s="7"/>
       <c r="V185" s="7"/>
     </row>
-    <row r="186" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B186" s="7"/>
       <c r="V186" s="7"/>
     </row>
-    <row r="187" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B187" s="7"/>
       <c r="V187" s="7"/>
     </row>
-    <row r="188" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B188" s="7"/>
       <c r="V188" s="7"/>
     </row>
-    <row r="189" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B189" s="7"/>
       <c r="V189" s="7"/>
     </row>
-    <row r="190" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B190" s="7"/>
       <c r="V190" s="7"/>
     </row>
-    <row r="191" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B191" s="7"/>
       <c r="V191" s="7"/>
     </row>
-    <row r="192" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B192" s="7"/>
       <c r="V192" s="7"/>
     </row>
@@ -11864,19 +12715,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{5E09103F-18DA-41D8-AADC-051314F72875}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{AACD03BA-7110-470B-8FD6-645E3ABDFC6C}">
       <formula1>"Preço, Prazo de entrega, Condição de Pagamento, Quantidade, Sem Retorno, Optou por outro produto"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{A64244E1-75E5-47BB-97FC-337746BC6580}">
+    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{4A729291-8881-4CFF-BB4A-C13BD6400CFA}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{A8596BA2-E648-420A-AD3D-9C5FC00EE59F}">
+    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{BB6D294B-C5DC-46C2-A29F-971CFAED38F9}">
       <formula1>"AC,AL,AP,AM,BA,CE,DF,ES,GO,MA,MT,MS,MG,PA,PB,PR,PE,PI,RJ,RN,RS,RO,RR,SC,SP,SE,TO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{3DAD7F24-4560-47CE-A770-E0B61F91C11C}">
+    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{8875CEC7-0CCF-49BE-B0DF-511ED9D01184}">
       <formula1>"Mínima,2ª Opção,3ª Opção,-"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{060C5511-3C88-4FF3-A683-017CD1ACCE6F}">
+    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{3CA3384B-299B-4E8A-9C30-CAF19506E8B1}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,Rascunho"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Base_Orcamentos.xlsx
+++ b/Base_Orcamentos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Orcamento\CONTROLE DE ORÇAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D6D0CAE-A8D5-49A7-B9F1-E572334D1DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AB5157F-2C6C-433E-AB90-CB369597AF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{035846D1-255F-4666-8D29-8D700277EFF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E3E6717E-C818-4F33-B2BA-57361DA08C0E}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Orcamentos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base_Orcamentos!$A$2:$X$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base_Orcamentos!$A$2:$X$182</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="454">
   <si>
     <t>Nº Orçamento</t>
   </si>
@@ -1395,6 +1395,15 @@
   </si>
   <si>
     <t>ETIQ 65mm X 225mm X 1 C | 236 M  c/ 1030 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100508</t>
+  </si>
+  <si>
+    <t>ORC 26100509</t>
+  </si>
+  <si>
+    <t>ETIQ 45mm X 45mm X 1 C | 48 M  c/ 1000 ETIQ</t>
   </si>
 </sst>
 </file>
@@ -1807,7 +1816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B5D822-AABD-4EAF-B56D-791DC31203AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F31AA38-AAD8-4F5E-803D-F2F768D09A91}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:X390"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1839,10 +1848,10 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q1" s="8">
-        <v>178977.62</v>
+        <v>277550.93</v>
       </c>
       <c r="R1" s="8">
-        <v>1494838.36</v>
+        <v>1502611.99</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="30" x14ac:dyDescent="0.25">
@@ -2992,13 +3001,16 @@
         <v>17888.37</v>
       </c>
       <c r="Q22" s="8">
-        <v>0</v>
+        <v>17888.37</v>
       </c>
       <c r="R22" s="8">
         <v>17888.37</v>
       </c>
       <c r="S22" t="s">
         <v>93</v>
+      </c>
+      <c r="T22" t="s">
+        <v>44</v>
       </c>
       <c r="U22" t="s">
         <v>94</v>
@@ -3856,13 +3868,16 @@
         <v>1846.78</v>
       </c>
       <c r="Q38" s="8">
-        <v>0</v>
+        <v>1846.78</v>
       </c>
       <c r="R38" s="8">
         <v>1846.78</v>
       </c>
       <c r="S38" t="s">
         <v>43</v>
+      </c>
+      <c r="T38" t="s">
+        <v>44</v>
       </c>
       <c r="V38" s="7"/>
     </row>
@@ -5613,13 +5628,16 @@
         <v>0</v>
       </c>
       <c r="Q69" s="8">
-        <v>0</v>
+        <v>14245.65</v>
       </c>
       <c r="R69" s="8">
         <v>14245.65</v>
       </c>
       <c r="S69" t="s">
         <v>43</v>
+      </c>
+      <c r="T69" t="s">
+        <v>44</v>
       </c>
       <c r="V69" s="7"/>
     </row>
@@ -5670,13 +5688,16 @@
         <v>0</v>
       </c>
       <c r="Q70" s="8">
-        <v>0</v>
+        <v>3249.51</v>
       </c>
       <c r="R70" s="8">
         <v>4374.9799999999996</v>
       </c>
       <c r="S70" t="s">
         <v>43</v>
+      </c>
+      <c r="T70" t="s">
+        <v>44</v>
       </c>
       <c r="V70" s="7"/>
     </row>
@@ -5727,13 +5748,16 @@
         <v>0</v>
       </c>
       <c r="Q71" s="8">
-        <v>0</v>
+        <v>3129.06</v>
       </c>
       <c r="R71" s="8">
         <v>5925.93</v>
       </c>
       <c r="S71" t="s">
         <v>43</v>
+      </c>
+      <c r="T71" t="s">
+        <v>44</v>
       </c>
       <c r="V71" s="7"/>
     </row>
@@ -5784,13 +5808,16 @@
         <v>0</v>
       </c>
       <c r="Q72" s="8">
-        <v>0</v>
+        <v>3593.6</v>
       </c>
       <c r="R72" s="8">
         <v>4147</v>
       </c>
       <c r="S72" t="s">
         <v>43</v>
+      </c>
+      <c r="T72" t="s">
+        <v>44</v>
       </c>
       <c r="V72" s="7"/>
     </row>
@@ -5838,13 +5865,16 @@
         <v>0</v>
       </c>
       <c r="Q73" s="8">
-        <v>0</v>
+        <v>4317.3</v>
       </c>
       <c r="R73" s="8">
         <v>4317.3</v>
       </c>
       <c r="S73" t="s">
         <v>43</v>
+      </c>
+      <c r="T73" t="s">
+        <v>44</v>
       </c>
       <c r="V73" s="7"/>
     </row>
@@ -5895,13 +5925,16 @@
         <v>0</v>
       </c>
       <c r="Q74" s="8">
-        <v>0</v>
+        <v>9888</v>
       </c>
       <c r="R74" s="8">
         <v>11527.8</v>
       </c>
       <c r="S74" t="s">
         <v>43</v>
+      </c>
+      <c r="T74" t="s">
+        <v>44</v>
       </c>
       <c r="V74" s="7"/>
     </row>
@@ -5949,13 +5982,16 @@
         <v>0</v>
       </c>
       <c r="Q75" s="8">
-        <v>0</v>
+        <v>13777.2</v>
       </c>
       <c r="R75" s="8">
         <v>13777.2</v>
       </c>
       <c r="S75" t="s">
         <v>43</v>
+      </c>
+      <c r="T75" t="s">
+        <v>44</v>
       </c>
       <c r="V75" s="7"/>
     </row>
@@ -6003,13 +6039,16 @@
         <v>0</v>
       </c>
       <c r="Q76" s="8">
-        <v>0</v>
+        <v>4372.3999999999996</v>
       </c>
       <c r="R76" s="8">
         <v>4372.3999999999996</v>
       </c>
       <c r="S76" t="s">
         <v>43</v>
+      </c>
+      <c r="T76" t="s">
+        <v>44</v>
       </c>
       <c r="V76" s="7"/>
     </row>
@@ -6057,13 +6096,16 @@
         <v>0</v>
       </c>
       <c r="Q77" s="8">
-        <v>0</v>
+        <v>11747.41</v>
       </c>
       <c r="R77" s="8">
         <v>11747.41</v>
       </c>
       <c r="S77" t="s">
         <v>43</v>
+      </c>
+      <c r="T77" t="s">
+        <v>44</v>
       </c>
       <c r="V77" s="7"/>
     </row>
@@ -6111,13 +6153,16 @@
         <v>0</v>
       </c>
       <c r="Q78" s="8">
-        <v>0</v>
+        <v>4699.08</v>
       </c>
       <c r="R78" s="8">
         <v>4699.08</v>
       </c>
       <c r="S78" t="s">
         <v>43</v>
+      </c>
+      <c r="T78" t="s">
+        <v>44</v>
       </c>
       <c r="V78" s="7"/>
     </row>
@@ -6165,13 +6210,16 @@
         <v>0</v>
       </c>
       <c r="Q79" s="8">
-        <v>0</v>
+        <v>2924.1</v>
       </c>
       <c r="R79" s="8">
         <v>2924.1</v>
       </c>
       <c r="S79" t="s">
         <v>43</v>
+      </c>
+      <c r="T79" t="s">
+        <v>44</v>
       </c>
       <c r="V79" s="7"/>
     </row>
@@ -6219,13 +6267,16 @@
         <v>0</v>
       </c>
       <c r="Q80" s="8">
-        <v>0</v>
+        <v>2894.85</v>
       </c>
       <c r="R80" s="8">
         <v>2924.1</v>
       </c>
       <c r="S80" t="s">
         <v>43</v>
+      </c>
+      <c r="T80" t="s">
+        <v>44</v>
       </c>
       <c r="V80" s="7"/>
     </row>
@@ -11487,7 +11538,7 @@
         <v>421</v>
       </c>
       <c r="B174" s="7">
-        <v>46297.730497685188</v>
+        <v>46300.417708333334</v>
       </c>
       <c r="C174" t="s">
         <v>422</v>
@@ -11508,19 +11559,19 @@
         <v>500</v>
       </c>
       <c r="I174" s="8">
-        <v>38.75</v>
+        <v>33.21</v>
       </c>
       <c r="J174" s="8">
-        <v>19375</v>
+        <v>16605</v>
       </c>
       <c r="K174" s="1">
         <v>1000</v>
       </c>
       <c r="L174" s="8">
-        <v>30.78</v>
+        <v>26.37</v>
       </c>
       <c r="M174" s="8">
-        <v>30780</v>
+        <v>26370</v>
       </c>
       <c r="N174" s="1">
         <v>0</v>
@@ -11535,7 +11586,7 @@
         <v>0</v>
       </c>
       <c r="R174" s="8">
-        <v>25077.5</v>
+        <v>21487.5</v>
       </c>
       <c r="V174" s="7"/>
     </row>
@@ -11996,11 +12047,117 @@
       <c r="V182" s="7"/>
     </row>
     <row r="183" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B183" s="7"/>
+      <c r="A183" t="s">
+        <v>451</v>
+      </c>
+      <c r="B183" s="7">
+        <v>46300.4137962963</v>
+      </c>
+      <c r="C183" t="s">
+        <v>439</v>
+      </c>
+      <c r="D183" t="s">
+        <v>26</v>
+      </c>
+      <c r="E183" t="s">
+        <v>119</v>
+      </c>
+      <c r="F183" t="s">
+        <v>440</v>
+      </c>
+      <c r="G183" t="s">
+        <v>441</v>
+      </c>
+      <c r="H183" s="1">
+        <v>100</v>
+      </c>
+      <c r="I183" s="8">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="J183" s="8">
+        <v>6610</v>
+      </c>
+      <c r="K183" s="1">
+        <v>150</v>
+      </c>
+      <c r="L183" s="8">
+        <v>57.01</v>
+      </c>
+      <c r="M183" s="8">
+        <v>8551.5</v>
+      </c>
+      <c r="N183" s="1">
+        <v>200</v>
+      </c>
+      <c r="O183" s="8">
+        <v>51.7</v>
+      </c>
+      <c r="P183" s="8">
+        <v>10340</v>
+      </c>
+      <c r="Q183" s="8">
+        <v>0</v>
+      </c>
+      <c r="R183" s="8">
+        <v>8500.5</v>
+      </c>
       <c r="V183" s="7"/>
     </row>
     <row r="184" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B184" s="7"/>
+      <c r="A184" t="s">
+        <v>452</v>
+      </c>
+      <c r="B184" s="7">
+        <v>46300.449606481481</v>
+      </c>
+      <c r="C184" t="s">
+        <v>443</v>
+      </c>
+      <c r="D184" t="s">
+        <v>260</v>
+      </c>
+      <c r="E184" t="s">
+        <v>444</v>
+      </c>
+      <c r="F184" t="s">
+        <v>453</v>
+      </c>
+      <c r="G184" t="s">
+        <v>33</v>
+      </c>
+      <c r="H184" s="1">
+        <v>80</v>
+      </c>
+      <c r="I184" s="8">
+        <v>30.67</v>
+      </c>
+      <c r="J184" s="8">
+        <v>2453.6</v>
+      </c>
+      <c r="K184" s="1">
+        <v>110</v>
+      </c>
+      <c r="L184" s="8">
+        <v>25.48</v>
+      </c>
+      <c r="M184" s="8">
+        <v>2802.8</v>
+      </c>
+      <c r="N184" s="1">
+        <v>150</v>
+      </c>
+      <c r="O184" s="8">
+        <v>22.22</v>
+      </c>
+      <c r="P184" s="8">
+        <v>3333</v>
+      </c>
+      <c r="Q184" s="8">
+        <v>0</v>
+      </c>
+      <c r="R184" s="8">
+        <v>2863.13</v>
+      </c>
       <c r="V184" s="7"/>
     </row>
     <row r="185" spans="1:22" x14ac:dyDescent="0.25">
@@ -12715,19 +12872,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{AACD03BA-7110-470B-8FD6-645E3ABDFC6C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{9CFF73C2-84EE-4A85-AB10-7E01AA20B210}">
       <formula1>"Preço, Prazo de entrega, Condição de Pagamento, Quantidade, Sem Retorno, Optou por outro produto"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{4A729291-8881-4CFF-BB4A-C13BD6400CFA}">
+    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{B5FD3375-2121-4CD8-B111-4B771D517F98}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{BB6D294B-C5DC-46C2-A29F-971CFAED38F9}">
+    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{32E1F199-FA4A-4117-AA05-67773CE5D3F8}">
       <formula1>"AC,AL,AP,AM,BA,CE,DF,ES,GO,MA,MT,MS,MG,PA,PB,PR,PE,PI,RJ,RN,RS,RO,RR,SC,SP,SE,TO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{8875CEC7-0CCF-49BE-B0DF-511ED9D01184}">
+    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{1768257F-FC7D-466F-A0F7-EDD204B79C15}">
       <formula1>"Mínima,2ª Opção,3ª Opção,-"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{3CA3384B-299B-4E8A-9C30-CAF19506E8B1}">
+    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{DA8BF5D6-EBB6-4184-AB73-4CF8584C86A9}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,Rascunho"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Base_Orcamentos.xlsx
+++ b/Base_Orcamentos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Orcamento\CONTROLE DE ORÇAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AB5157F-2C6C-433E-AB90-CB369597AF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{627B8CB7-CB02-4B55-9400-984C9BAF189D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E3E6717E-C818-4F33-B2BA-57361DA08C0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{03EDBE0E-5D2C-4BCF-936C-AE9D27225874}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Orcamentos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base_Orcamentos!$A$2:$X$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base_Orcamentos!$A$2:$X$184</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1400,7 +1400,7 @@
     <t>ORC 26100508</t>
   </si>
   <si>
-    <t>ORC 26100509</t>
+    <t>ORC 26100510</t>
   </si>
   <si>
     <t>ETIQ 45mm X 45mm X 1 C | 48 M  c/ 1000 ETIQ</t>
@@ -1816,7 +1816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F31AA38-AAD8-4F5E-803D-F2F768D09A91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC55B02-5C37-414D-A779-34EC3E3B6D07}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:X390"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1851,7 +1851,7 @@
         <v>277550.93</v>
       </c>
       <c r="R1" s="8">
-        <v>1502611.99</v>
+        <v>1503082.02</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="30" x14ac:dyDescent="0.25">
@@ -11880,7 +11880,7 @@
         <v>442</v>
       </c>
       <c r="B180" s="7">
-        <v>46300.362326388888</v>
+        <v>46300.473171296297</v>
       </c>
       <c r="C180" t="s">
         <v>443</v>
@@ -11937,7 +11937,7 @@
         <v>442</v>
       </c>
       <c r="B181" s="7">
-        <v>46300.362326388888</v>
+        <v>46300.473171296297</v>
       </c>
       <c r="C181" t="s">
         <v>443</v>
@@ -12108,7 +12108,7 @@
         <v>452</v>
       </c>
       <c r="B184" s="7">
-        <v>46300.449606481481</v>
+        <v>46300.472534722219</v>
       </c>
       <c r="C184" t="s">
         <v>443</v>
@@ -12126,37 +12126,37 @@
         <v>33</v>
       </c>
       <c r="H184" s="1">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="I184" s="8">
-        <v>30.67</v>
+        <v>26.78</v>
       </c>
       <c r="J184" s="8">
-        <v>2453.6</v>
+        <v>2811.9</v>
       </c>
       <c r="K184" s="1">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="L184" s="8">
-        <v>25.48</v>
+        <v>23.41</v>
       </c>
       <c r="M184" s="8">
-        <v>2802.8</v>
+        <v>3277.4</v>
       </c>
       <c r="N184" s="1">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="O184" s="8">
-        <v>22.22</v>
+        <v>20.58</v>
       </c>
       <c r="P184" s="8">
-        <v>3333</v>
+        <v>3910.2</v>
       </c>
       <c r="Q184" s="8">
         <v>0</v>
       </c>
       <c r="R184" s="8">
-        <v>2863.13</v>
+        <v>3333.17</v>
       </c>
       <c r="V184" s="7"/>
     </row>
@@ -12872,19 +12872,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{9CFF73C2-84EE-4A85-AB10-7E01AA20B210}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{EF5C7CF5-8C00-456C-8DD8-5ABF8D289361}">
       <formula1>"Preço, Prazo de entrega, Condição de Pagamento, Quantidade, Sem Retorno, Optou por outro produto"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{B5FD3375-2121-4CD8-B111-4B771D517F98}">
+    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{DF4BDE76-4E03-42FA-9D27-A355FF8DF3F9}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{32E1F199-FA4A-4117-AA05-67773CE5D3F8}">
+    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{3D64CA54-2F7A-41F3-8D0F-B4B869F30452}">
       <formula1>"AC,AL,AP,AM,BA,CE,DF,ES,GO,MA,MT,MS,MG,PA,PB,PR,PE,PI,RJ,RN,RS,RO,RR,SC,SP,SE,TO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{1768257F-FC7D-466F-A0F7-EDD204B79C15}">
+    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{20E7D180-E016-4003-8150-66FA3A201DC3}">
       <formula1>"Mínima,2ª Opção,3ª Opção,-"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{DA8BF5D6-EBB6-4184-AB73-4CF8584C86A9}">
+    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{3E729798-59A8-4ECF-9EB5-CF706C90FF98}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,Rascunho"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Base_Orcamentos.xlsx
+++ b/Base_Orcamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Orcamento\CONTROLE DE ORÇAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{627B8CB7-CB02-4B55-9400-984C9BAF189D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EA9DA29-BEFB-4D5C-91E7-D73D87409546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{03EDBE0E-5D2C-4BCF-936C-AE9D27225874}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{78492AB0-D603-45B8-AB23-C2A7B43B86A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Orcamentos" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="450">
   <si>
     <t>Nº Orçamento</t>
   </si>
@@ -1013,9 +1013,6 @@
     <t>VILA DAS FRUTAS</t>
   </si>
   <si>
-    <t>EDEVALDO</t>
-  </si>
-  <si>
     <t>ETIQ 60mm X 120mm X 2 C | 62 M  c/ 500 ETIQ</t>
   </si>
   <si>
@@ -1163,9 +1160,6 @@
     <t>M A FRENA &amp; CIA LTDA – SUPER KIKO</t>
   </si>
   <si>
-    <t>WALDENIR</t>
-  </si>
-  <si>
     <t>ETIQ 70mm X 70mm X 1 C | METRAGEM A DEFINIR</t>
   </si>
   <si>
@@ -1307,7 +1301,85 @@
     <t>ETIQ 33mm X 21mm X 3 C | 30 M  c/ 1250 ETIQ</t>
   </si>
   <si>
-    <t>ORC 26100208</t>
+    <t>ORC 26100501</t>
+  </si>
+  <si>
+    <t>GW PRIME COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>ETIQ 50mm X 30mm X 2 C | 49,5 M  c/ 3000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100502</t>
+  </si>
+  <si>
+    <t>CAPS CORP COMERCIO DE ARTIGOS OPTICOS LTDA</t>
+  </si>
+  <si>
+    <t>ETIQ 40mm X 40mm X 1 C | 21,5 M  c/ 500 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100503</t>
+  </si>
+  <si>
+    <t>SUERMERCADO BOM LAMI</t>
+  </si>
+  <si>
+    <t>ETIQ 40mm X 60mm X 1 C | 63 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100504</t>
+  </si>
+  <si>
+    <t>MASSA PURA</t>
+  </si>
+  <si>
+    <t>ETIQ 60mm X 100mm X 1 C | 103 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100505</t>
+  </si>
+  <si>
+    <t>BAR ZENAIDE</t>
+  </si>
+  <si>
+    <t>ETIQ 60mm X 40mm X 1 C | 40 M  c/ 930 ETIQ</t>
+  </si>
+  <si>
+    <t>A.52 BOPP Térmico</t>
+  </si>
+  <si>
+    <t>ORC 26100506</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO DORENSE</t>
+  </si>
+  <si>
+    <t>GERALDO</t>
+  </si>
+  <si>
+    <t>ETIQ 60mm X 125mm X 1 C | 128 M  c/ 1000 ETIQ</t>
+  </si>
+  <si>
+    <t>LACRE 90mm X 190mm X 1 C | 193 M  c/ 1000 LACRE</t>
+  </si>
+  <si>
+    <t>ORC 26100507</t>
+  </si>
+  <si>
+    <t>DOMENICHELLI</t>
+  </si>
+  <si>
+    <t>ETIQ 65mm X 225mm X 1 C | 236 M  c/ 1030 ETIQ</t>
+  </si>
+  <si>
+    <t>ORC 26100508</t>
+  </si>
+  <si>
+    <t>ORC 26100510</t>
+  </si>
+  <si>
+    <t>ETIQ 45mm X 45mm X 1 C | 48 M  c/ 1000 ETIQ</t>
   </si>
   <si>
     <t>LÍDER COMÉRCIO</t>
@@ -1320,90 +1392,6 @@
   </si>
   <si>
     <t>ETIQ 79mm X 95mm X 1 C | 45 M  c/ 450 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26100501</t>
-  </si>
-  <si>
-    <t>GW PRIME COMERCIO E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>ETIQ 50mm X 30mm X 2 C | 49,5 M  c/ 3000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26100502</t>
-  </si>
-  <si>
-    <t>CAPS CORP COMERCIO DE ARTIGOS OPTICOS LTDA</t>
-  </si>
-  <si>
-    <t>ETIQ 40mm X 40mm X 1 C | 21,5 M  c/ 500 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26100503</t>
-  </si>
-  <si>
-    <t>SUERMERCADO BOM LAMI</t>
-  </si>
-  <si>
-    <t>ETIQ 40mm X 60mm X 1 C | 63 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26100504</t>
-  </si>
-  <si>
-    <t>MASSA PURA</t>
-  </si>
-  <si>
-    <t>ETIQ 60mm X 100mm X 1 C | 103 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26100505</t>
-  </si>
-  <si>
-    <t>BAR ZENAIDE</t>
-  </si>
-  <si>
-    <t>ETIQ 60mm X 40mm X 1 C | 40 M  c/ 930 ETIQ</t>
-  </si>
-  <si>
-    <t>A.52 BOPP Térmico</t>
-  </si>
-  <si>
-    <t>ORC 26100506</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO DORENSE</t>
-  </si>
-  <si>
-    <t>GERALDO</t>
-  </si>
-  <si>
-    <t>ETIQ 60mm X 125mm X 1 C | 128 M  c/ 1000 ETIQ</t>
-  </si>
-  <si>
-    <t>LACRE 90mm X 190mm X 1 C | 193 M  c/ 1000 LACRE</t>
-  </si>
-  <si>
-    <t>ORC 26100507</t>
-  </si>
-  <si>
-    <t>DOMENICHELLI</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>ETIQ 65mm X 225mm X 1 C | 236 M  c/ 1030 ETIQ</t>
-  </si>
-  <si>
-    <t>ORC 26100508</t>
-  </si>
-  <si>
-    <t>ORC 26100510</t>
-  </si>
-  <si>
-    <t>ETIQ 45mm X 45mm X 1 C | 48 M  c/ 1000 ETIQ</t>
   </si>
 </sst>
 </file>
@@ -1816,7 +1804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC55B02-5C37-414D-A779-34EC3E3B6D07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EED4DDA-A51D-4172-8280-3B078B5CEAFC}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:X390"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4747,7 +4735,7 @@
         <v>3985.14</v>
       </c>
       <c r="S53" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="T53" t="s">
         <v>44</v>
@@ -8487,7 +8475,7 @@
         <v>321</v>
       </c>
       <c r="B120" s="7">
-        <v>46282.705983796295</v>
+        <v>46300.636435185188</v>
       </c>
       <c r="C120" t="s">
         <v>322</v>
@@ -8496,10 +8484,10 @@
         <v>26</v>
       </c>
       <c r="E120" t="s">
+        <v>185</v>
+      </c>
+      <c r="F120" t="s">
         <v>323</v>
-      </c>
-      <c r="F120" t="s">
-        <v>324</v>
       </c>
       <c r="G120" t="s">
         <v>29</v>
@@ -8541,13 +8529,13 @@
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B121" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C121" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D121" t="s">
         <v>26</v>
@@ -8556,7 +8544,7 @@
         <v>27</v>
       </c>
       <c r="F121" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G121" t="s">
         <v>29</v>
@@ -8598,13 +8586,13 @@
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B122" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C122" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D122" t="s">
         <v>26</v>
@@ -8613,7 +8601,7 @@
         <v>27</v>
       </c>
       <c r="F122" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G122" t="s">
         <v>29</v>
@@ -8655,13 +8643,13 @@
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B123" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C123" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D123" t="s">
         <v>26</v>
@@ -8670,7 +8658,7 @@
         <v>27</v>
       </c>
       <c r="F123" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G123" t="s">
         <v>29</v>
@@ -8712,13 +8700,13 @@
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B124" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C124" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D124" t="s">
         <v>26</v>
@@ -8727,7 +8715,7 @@
         <v>27</v>
       </c>
       <c r="F124" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G124" t="s">
         <v>29</v>
@@ -8769,13 +8757,13 @@
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B125" s="7">
         <v>46283.420798611114</v>
       </c>
       <c r="C125" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D125" t="s">
         <v>26</v>
@@ -8784,7 +8772,7 @@
         <v>27</v>
       </c>
       <c r="F125" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G125" t="s">
         <v>29</v>
@@ -8826,13 +8814,13 @@
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B126" s="7">
         <v>46287.540856481479</v>
       </c>
       <c r="C126" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D126" t="s">
         <v>26</v>
@@ -8841,7 +8829,7 @@
         <v>47</v>
       </c>
       <c r="F126" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G126" t="s">
         <v>142</v>
@@ -8883,13 +8871,13 @@
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B127" s="7">
         <v>46287.540856481479</v>
       </c>
       <c r="C127" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D127" t="s">
         <v>26</v>
@@ -8898,7 +8886,7 @@
         <v>47</v>
       </c>
       <c r="F127" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G127" t="s">
         <v>142</v>
@@ -8940,22 +8928,22 @@
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B128" s="7">
         <v>46287.66646990741</v>
       </c>
       <c r="C128" t="s">
+        <v>336</v>
+      </c>
+      <c r="D128" t="s">
         <v>337</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>338</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>339</v>
-      </c>
-      <c r="F128" t="s">
-        <v>340</v>
       </c>
       <c r="G128" t="s">
         <v>199</v>
@@ -8997,22 +8985,22 @@
     </row>
     <row r="129" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B129" s="7">
         <v>46287.66646990741</v>
       </c>
       <c r="C129" t="s">
+        <v>336</v>
+      </c>
+      <c r="D129" t="s">
         <v>337</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>338</v>
       </c>
-      <c r="E129" t="s">
-        <v>339</v>
-      </c>
       <c r="F129" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G129" t="s">
         <v>33</v>
@@ -9054,22 +9042,22 @@
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B130" s="7">
         <v>46287.66646990741</v>
       </c>
       <c r="C130" t="s">
+        <v>336</v>
+      </c>
+      <c r="D130" t="s">
         <v>337</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
         <v>338</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>339</v>
-      </c>
-      <c r="F130" t="s">
-        <v>340</v>
       </c>
       <c r="G130" t="s">
         <v>199</v>
@@ -9111,22 +9099,22 @@
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B131" s="7">
         <v>46287.649074074077</v>
       </c>
       <c r="C131" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D131" t="s">
         <v>247</v>
       </c>
       <c r="E131" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F131" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G131" t="s">
         <v>33</v>
@@ -9168,13 +9156,13 @@
     </row>
     <row r="132" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B132" s="7">
         <v>46287.644872685189</v>
       </c>
       <c r="C132" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D132" t="s">
         <v>256</v>
@@ -9183,7 +9171,7 @@
         <v>176</v>
       </c>
       <c r="F132" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G132" t="s">
         <v>142</v>
@@ -9225,7 +9213,7 @@
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B133" s="7">
         <v>46288.702326388891</v>
@@ -9282,22 +9270,22 @@
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B134" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C134" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D134" t="s">
         <v>26</v>
       </c>
       <c r="E134" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F134" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G134" t="s">
         <v>33</v>
@@ -9339,22 +9327,22 @@
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B135" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C135" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D135" t="s">
         <v>26</v>
       </c>
       <c r="E135" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F135" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G135" t="s">
         <v>33</v>
@@ -9396,22 +9384,22 @@
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B136" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C136" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D136" t="s">
         <v>26</v>
       </c>
       <c r="E136" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F136" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G136" t="s">
         <v>199</v>
@@ -9453,22 +9441,22 @@
     </row>
     <row r="137" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B137" s="7">
         <v>46288.490717592591</v>
       </c>
       <c r="C137" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D137" t="s">
         <v>26</v>
       </c>
       <c r="E137" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F137" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G137" t="s">
         <v>199</v>
@@ -9504,13 +9492,13 @@
     </row>
     <row r="138" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B138" s="7">
         <v>46288.70853009259</v>
       </c>
       <c r="C138" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D138" t="s">
         <v>26</v>
@@ -9519,7 +9507,7 @@
         <v>41</v>
       </c>
       <c r="F138" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G138" t="s">
         <v>92</v>
@@ -9561,13 +9549,13 @@
     </row>
     <row r="139" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B139" s="7">
         <v>46289.572893518518</v>
       </c>
       <c r="C139" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D139" t="s">
         <v>26</v>
@@ -9576,7 +9564,7 @@
         <v>58</v>
       </c>
       <c r="F139" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G139" t="s">
         <v>29</v>
@@ -9618,13 +9606,13 @@
     </row>
     <row r="140" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B140" s="7">
         <v>46289.569641203707</v>
       </c>
       <c r="C140" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D140" t="s">
         <v>26</v>
@@ -9633,7 +9621,7 @@
         <v>62</v>
       </c>
       <c r="F140" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G140" t="s">
         <v>33</v>
@@ -9675,13 +9663,13 @@
     </row>
     <row r="141" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B141" s="7">
         <v>46289.567453703705</v>
       </c>
       <c r="C141" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D141" t="s">
         <v>26</v>
@@ -9690,7 +9678,7 @@
         <v>58</v>
       </c>
       <c r="F141" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G141" t="s">
         <v>70</v>
@@ -9732,13 +9720,13 @@
     </row>
     <row r="142" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B142" s="7">
         <v>46289.571481481478</v>
       </c>
       <c r="C142" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D142" t="s">
         <v>247</v>
@@ -9747,7 +9735,7 @@
         <v>119</v>
       </c>
       <c r="F142" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G142" t="s">
         <v>29</v>
@@ -9789,22 +9777,22 @@
     </row>
     <row r="143" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B143" s="7">
         <v>46289.718541666669</v>
       </c>
       <c r="C143" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D143" t="s">
         <v>26</v>
       </c>
       <c r="E143" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F143" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G143" t="s">
         <v>199</v>
@@ -9846,22 +9834,22 @@
     </row>
     <row r="144" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B144" s="7">
         <v>46289.718541666669</v>
       </c>
       <c r="C144" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D144" t="s">
         <v>26</v>
       </c>
       <c r="E144" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F144" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G144" t="s">
         <v>199</v>
@@ -9903,22 +9891,22 @@
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>370</v>
+      </c>
+      <c r="B145" s="7">
+        <v>46300.631956018522</v>
+      </c>
+      <c r="C145" t="s">
         <v>371</v>
-      </c>
-      <c r="B145" s="7">
-        <v>46290.663263888891</v>
-      </c>
-      <c r="C145" t="s">
-        <v>372</v>
       </c>
       <c r="D145" t="s">
         <v>124</v>
       </c>
       <c r="E145" t="s">
-        <v>373</v>
+        <v>163</v>
       </c>
       <c r="F145" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G145" t="s">
         <v>33</v>
@@ -9960,22 +9948,22 @@
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>370</v>
+      </c>
+      <c r="B146" s="7">
+        <v>46300.631956018522</v>
+      </c>
+      <c r="C146" t="s">
         <v>371</v>
-      </c>
-      <c r="B146" s="7">
-        <v>46290.663263888891</v>
-      </c>
-      <c r="C146" t="s">
-        <v>372</v>
       </c>
       <c r="D146" t="s">
         <v>124</v>
       </c>
       <c r="E146" t="s">
-        <v>373</v>
+        <v>163</v>
       </c>
       <c r="F146" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G146" t="s">
         <v>64</v>
@@ -10017,13 +10005,13 @@
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B147" s="7">
-        <v>46295.710763888892</v>
+        <v>46300.631574074076</v>
       </c>
       <c r="C147" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D147" t="s">
         <v>26</v>
@@ -10032,7 +10020,7 @@
         <v>172</v>
       </c>
       <c r="F147" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G147" t="s">
         <v>33</v>
@@ -10074,13 +10062,13 @@
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B148" s="7">
         <v>46294.695925925924</v>
       </c>
       <c r="C148" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D148" t="s">
         <v>26</v>
@@ -10089,7 +10077,7 @@
         <v>167</v>
       </c>
       <c r="F148" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H148" s="1">
         <v>72</v>
@@ -10128,13 +10116,13 @@
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B149" s="7">
         <v>46295.662303240744</v>
       </c>
       <c r="C149" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D149" t="s">
         <v>256</v>
@@ -10143,7 +10131,7 @@
         <v>176</v>
       </c>
       <c r="F149" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G149" t="s">
         <v>70</v>
@@ -10185,13 +10173,13 @@
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B150" s="7">
         <v>46295.662303240744</v>
       </c>
       <c r="C150" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D150" t="s">
         <v>256</v>
@@ -10200,7 +10188,7 @@
         <v>176</v>
       </c>
       <c r="F150" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G150" t="s">
         <v>33</v>
@@ -10242,13 +10230,13 @@
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B151" s="7">
         <v>46295.662303240744</v>
       </c>
       <c r="C151" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D151" t="s">
         <v>256</v>
@@ -10257,7 +10245,7 @@
         <v>176</v>
       </c>
       <c r="F151" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G151" t="s">
         <v>64</v>
@@ -10299,22 +10287,22 @@
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B152" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C152" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D152" t="s">
         <v>256</v>
       </c>
       <c r="E152" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F152" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G152" t="s">
         <v>33</v>
@@ -10356,22 +10344,22 @@
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B153" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C153" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D153" t="s">
         <v>256</v>
       </c>
       <c r="E153" t="s">
+        <v>386</v>
+      </c>
+      <c r="F153" t="s">
         <v>388</v>
-      </c>
-      <c r="F153" t="s">
-        <v>390</v>
       </c>
       <c r="G153" t="s">
         <v>64</v>
@@ -10413,22 +10401,22 @@
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B154" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C154" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D154" t="s">
         <v>256</v>
       </c>
       <c r="E154" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F154" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G154" t="s">
         <v>33</v>
@@ -10470,22 +10458,22 @@
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B155" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C155" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D155" t="s">
         <v>256</v>
       </c>
       <c r="E155" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F155" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G155" t="s">
         <v>33</v>
@@ -10527,22 +10515,22 @@
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B156" s="7">
         <v>46295.662824074076</v>
       </c>
       <c r="C156" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D156" t="s">
         <v>256</v>
       </c>
       <c r="E156" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F156" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G156" t="s">
         <v>64</v>
@@ -10584,22 +10572,22 @@
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B157" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C157" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D157" t="s">
         <v>256</v>
       </c>
       <c r="E157" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F157" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G157" t="s">
         <v>33</v>
@@ -10641,22 +10629,22 @@
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B158" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C158" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D158" t="s">
         <v>256</v>
       </c>
       <c r="E158" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F158" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G158" t="s">
         <v>64</v>
@@ -10698,22 +10686,22 @@
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B159" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C159" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D159" t="s">
         <v>256</v>
       </c>
       <c r="E159" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F159" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G159" t="s">
         <v>64</v>
@@ -10755,25 +10743,25 @@
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B160" s="7">
         <v>46295.660590277781</v>
       </c>
       <c r="C160" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D160" t="s">
         <v>256</v>
       </c>
       <c r="E160" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F160" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G160" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H160" s="1">
         <v>130</v>
@@ -10812,13 +10800,13 @@
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B161" s="7">
         <v>46295.67895833333</v>
       </c>
       <c r="C161" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D161" t="s">
         <v>256</v>
@@ -10827,7 +10815,7 @@
         <v>140</v>
       </c>
       <c r="F161" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G161" t="s">
         <v>33</v>
@@ -10869,13 +10857,13 @@
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B162" s="7">
         <v>46295.67895833333</v>
       </c>
       <c r="C162" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D162" t="s">
         <v>256</v>
@@ -10884,7 +10872,7 @@
         <v>140</v>
       </c>
       <c r="F162" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G162" t="s">
         <v>70</v>
@@ -10926,13 +10914,13 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B163" s="7">
         <v>46295.67895833333</v>
       </c>
       <c r="C163" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D163" t="s">
         <v>256</v>
@@ -10941,7 +10929,7 @@
         <v>140</v>
       </c>
       <c r="F163" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G163" t="s">
         <v>33</v>
@@ -10983,19 +10971,19 @@
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B164" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C164" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D164" t="s">
         <v>256</v>
       </c>
       <c r="E164" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F164" t="s">
         <v>182</v>
@@ -11040,22 +11028,22 @@
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B165" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C165" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D165" t="s">
         <v>256</v>
       </c>
       <c r="E165" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F165" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G165" t="s">
         <v>114</v>
@@ -11097,22 +11085,22 @@
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B166" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C166" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D166" t="s">
         <v>256</v>
       </c>
       <c r="E166" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F166" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G166" t="s">
         <v>97</v>
@@ -11154,22 +11142,22 @@
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B167" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C167" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D167" t="s">
         <v>256</v>
       </c>
       <c r="E167" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F167" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G167" t="s">
         <v>70</v>
@@ -11211,22 +11199,22 @@
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B168" s="7">
         <v>46295.671307870369</v>
       </c>
       <c r="C168" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D168" t="s">
         <v>256</v>
       </c>
       <c r="E168" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F168" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G168" t="s">
         <v>29</v>
@@ -11268,22 +11256,22 @@
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B169" s="7">
         <v>46296.652222222219</v>
       </c>
       <c r="C169" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D169" t="s">
         <v>57</v>
       </c>
       <c r="E169" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F169" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G169" t="s">
         <v>199</v>
@@ -11325,7 +11313,7 @@
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B170" s="7">
         <v>46297.609618055554</v>
@@ -11340,7 +11328,7 @@
         <v>41</v>
       </c>
       <c r="F170" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G170" t="s">
         <v>33</v>
@@ -11364,22 +11352,22 @@
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B171" s="7">
         <v>46297.679155092592</v>
       </c>
       <c r="C171" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D171" t="s">
         <v>57</v>
       </c>
       <c r="E171" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F171" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G171" t="s">
         <v>70</v>
@@ -11421,22 +11409,22 @@
     </row>
     <row r="172" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B172" s="7">
         <v>46297.679155092592</v>
       </c>
       <c r="C172" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D172" t="s">
         <v>57</v>
       </c>
       <c r="E172" t="s">
+        <v>415</v>
+      </c>
+      <c r="F172" t="s">
         <v>417</v>
-      </c>
-      <c r="F172" t="s">
-        <v>419</v>
       </c>
       <c r="G172" t="s">
         <v>64</v>
@@ -11478,22 +11466,22 @@
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B173" s="7">
         <v>46297.679155092592</v>
       </c>
       <c r="C173" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D173" t="s">
         <v>57</v>
       </c>
       <c r="E173" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F173" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G173" t="s">
         <v>70</v>
@@ -11535,70 +11523,70 @@
     </row>
     <row r="174" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>419</v>
+      </c>
+      <c r="B174" s="7">
+        <v>46300.351354166669</v>
+      </c>
+      <c r="C174" t="s">
+        <v>420</v>
+      </c>
+      <c r="D174" t="s">
+        <v>26</v>
+      </c>
+      <c r="E174" t="s">
+        <v>62</v>
+      </c>
+      <c r="F174" t="s">
         <v>421</v>
       </c>
-      <c r="B174" s="7">
-        <v>46300.417708333334</v>
-      </c>
-      <c r="C174" t="s">
-        <v>422</v>
-      </c>
-      <c r="D174" t="s">
-        <v>423</v>
-      </c>
-      <c r="E174" t="s">
-        <v>424</v>
-      </c>
-      <c r="F174" t="s">
-        <v>425</v>
-      </c>
       <c r="G174" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H174" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I174" s="8">
-        <v>33.21</v>
+        <v>23.47</v>
       </c>
       <c r="J174" s="8">
-        <v>16605</v>
+        <v>2347</v>
       </c>
       <c r="K174" s="1">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="L174" s="8">
-        <v>26.37</v>
+        <v>21.18</v>
       </c>
       <c r="M174" s="8">
-        <v>26370</v>
+        <v>3177</v>
       </c>
       <c r="N174" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O174" s="8">
-        <v>0</v>
+        <v>20.43</v>
       </c>
       <c r="P174" s="8">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="Q174" s="8">
         <v>0</v>
       </c>
       <c r="R174" s="8">
-        <v>21487.5</v>
+        <v>3203.33</v>
       </c>
       <c r="V174" s="7"/>
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B175" s="7">
-        <v>46300.351354166669</v>
+        <v>46300.35019675926</v>
       </c>
       <c r="C175" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D175" t="s">
         <v>26</v>
@@ -11607,556 +11595,556 @@
         <v>62</v>
       </c>
       <c r="F175" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G175" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="H175" s="1">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="I175" s="8">
-        <v>23.47</v>
+        <v>18.5</v>
       </c>
       <c r="J175" s="8">
-        <v>2347</v>
+        <v>2960</v>
       </c>
       <c r="K175" s="1">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="L175" s="8">
-        <v>21.18</v>
+        <v>15.81</v>
       </c>
       <c r="M175" s="8">
-        <v>3177</v>
+        <v>3399.15</v>
       </c>
       <c r="N175" s="1">
-        <v>200</v>
+        <v>290</v>
       </c>
       <c r="O175" s="8">
-        <v>20.43</v>
+        <v>14.06</v>
       </c>
       <c r="P175" s="8">
-        <v>4086</v>
+        <v>4077.4</v>
       </c>
       <c r="Q175" s="8">
         <v>0</v>
       </c>
       <c r="R175" s="8">
-        <v>3203.33</v>
+        <v>3478.85</v>
       </c>
       <c r="V175" s="7"/>
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B176" s="7">
-        <v>46300.35019675926</v>
+        <v>46300.356377314813</v>
       </c>
       <c r="C176" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D176" t="s">
-        <v>26</v>
+        <v>247</v>
       </c>
       <c r="E176" t="s">
-        <v>62</v>
+        <v>292</v>
       </c>
       <c r="F176" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="G176" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="H176" s="1">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="I176" s="8">
-        <v>18.5</v>
+        <v>22.09</v>
       </c>
       <c r="J176" s="8">
-        <v>2960</v>
+        <v>2540.35</v>
       </c>
       <c r="K176" s="1">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="L176" s="8">
-        <v>15.81</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M176" s="8">
-        <v>3399.15</v>
+        <v>3162</v>
       </c>
       <c r="N176" s="1">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="O176" s="8">
-        <v>14.06</v>
+        <v>18.23</v>
       </c>
       <c r="P176" s="8">
-        <v>4077.4</v>
+        <v>3828.3</v>
       </c>
       <c r="Q176" s="8">
         <v>0</v>
       </c>
       <c r="R176" s="8">
-        <v>3478.85</v>
+        <v>3176.88</v>
       </c>
       <c r="V176" s="7"/>
     </row>
     <row r="177" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B177" s="7">
-        <v>46300.356377314813</v>
+        <v>46300.359131944446</v>
       </c>
       <c r="C177" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D177" t="s">
-        <v>247</v>
+        <v>124</v>
       </c>
       <c r="E177" t="s">
-        <v>292</v>
+        <v>176</v>
       </c>
       <c r="F177" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="G177" t="s">
         <v>33</v>
       </c>
       <c r="H177" s="1">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="I177" s="8">
-        <v>22.09</v>
+        <v>51.61</v>
       </c>
       <c r="J177" s="8">
-        <v>2540.35</v>
+        <v>2580.5</v>
       </c>
       <c r="K177" s="1">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="L177" s="8">
-        <v>20.399999999999999</v>
+        <v>47.16</v>
       </c>
       <c r="M177" s="8">
-        <v>3162</v>
+        <v>3301.2</v>
       </c>
       <c r="N177" s="1">
-        <v>210</v>
+        <v>95</v>
       </c>
       <c r="O177" s="8">
-        <v>18.23</v>
+        <v>43.12</v>
       </c>
       <c r="P177" s="8">
-        <v>3828.3</v>
+        <v>4096.3999999999996</v>
       </c>
       <c r="Q177" s="8">
         <v>0</v>
       </c>
       <c r="R177" s="8">
-        <v>3176.88</v>
+        <v>3326.03</v>
       </c>
       <c r="V177" s="7"/>
     </row>
     <row r="178" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B178" s="7">
-        <v>46300.359131944446</v>
+        <v>46300.384212962963</v>
       </c>
       <c r="C178" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D178" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="E178" t="s">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="F178" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="G178" t="s">
-        <v>33</v>
+        <v>434</v>
       </c>
       <c r="H178" s="1">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="I178" s="8">
-        <v>51.61</v>
+        <v>44.75</v>
       </c>
       <c r="J178" s="8">
-        <v>2580.5</v>
+        <v>22375</v>
       </c>
       <c r="K178" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L178" s="8">
-        <v>47.16</v>
+        <v>0</v>
       </c>
       <c r="M178" s="8">
-        <v>3301.2</v>
+        <v>0</v>
       </c>
       <c r="N178" s="1">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="O178" s="8">
-        <v>43.12</v>
+        <v>0</v>
       </c>
       <c r="P178" s="8">
-        <v>4096.3999999999996</v>
+        <v>0</v>
       </c>
       <c r="Q178" s="8">
         <v>0</v>
       </c>
       <c r="R178" s="8">
-        <v>3326.03</v>
+        <v>22375</v>
       </c>
       <c r="V178" s="7"/>
     </row>
     <row r="179" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>435</v>
+      </c>
+      <c r="B179" s="7">
+        <v>46300.473171296297</v>
+      </c>
+      <c r="C179" t="s">
+        <v>436</v>
+      </c>
+      <c r="D179" t="s">
+        <v>260</v>
+      </c>
+      <c r="E179" t="s">
+        <v>437</v>
+      </c>
+      <c r="F179" t="s">
         <v>438</v>
       </c>
-      <c r="B179" s="7">
-        <v>46300.384212962963</v>
-      </c>
-      <c r="C179" t="s">
-        <v>439</v>
-      </c>
-      <c r="D179" t="s">
-        <v>26</v>
-      </c>
-      <c r="E179" t="s">
-        <v>119</v>
-      </c>
-      <c r="F179" t="s">
-        <v>440</v>
-      </c>
       <c r="G179" t="s">
-        <v>441</v>
+        <v>33</v>
       </c>
       <c r="H179" s="1">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="I179" s="8">
-        <v>44.75</v>
+        <v>142.63999999999999</v>
       </c>
       <c r="J179" s="8">
-        <v>22375</v>
+        <v>2852.8</v>
       </c>
       <c r="K179" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L179" s="8">
-        <v>0</v>
+        <v>117.42</v>
       </c>
       <c r="M179" s="8">
-        <v>0</v>
+        <v>3522.6</v>
       </c>
       <c r="N179" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O179" s="8">
-        <v>0</v>
+        <v>81.96</v>
       </c>
       <c r="P179" s="8">
-        <v>0</v>
+        <v>3278.4</v>
       </c>
       <c r="Q179" s="8">
         <v>0</v>
       </c>
       <c r="R179" s="8">
-        <v>22375</v>
+        <v>3217.93</v>
       </c>
       <c r="V179" s="7"/>
     </row>
     <row r="180" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="B180" s="7">
         <v>46300.473171296297</v>
       </c>
       <c r="C180" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="D180" t="s">
         <v>260</v>
       </c>
       <c r="E180" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="F180" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="G180" t="s">
         <v>33</v>
       </c>
       <c r="H180" s="1">
+        <v>15</v>
+      </c>
+      <c r="I180" s="8">
+        <v>224.18</v>
+      </c>
+      <c r="J180" s="8">
+        <v>3362.7</v>
+      </c>
+      <c r="K180" s="1">
         <v>20</v>
       </c>
-      <c r="I180" s="8">
-        <v>142.63999999999999</v>
-      </c>
-      <c r="J180" s="8">
-        <v>2852.8</v>
-      </c>
-      <c r="K180" s="1">
+      <c r="L180" s="8">
+        <v>196.21</v>
+      </c>
+      <c r="M180" s="8">
+        <v>3924.2</v>
+      </c>
+      <c r="N180" s="1">
         <v>30</v>
       </c>
-      <c r="L180" s="8">
-        <v>117.42</v>
-      </c>
-      <c r="M180" s="8">
-        <v>3522.6</v>
-      </c>
-      <c r="N180" s="1">
-        <v>40</v>
-      </c>
       <c r="O180" s="8">
-        <v>81.96</v>
+        <v>167.13</v>
       </c>
       <c r="P180" s="8">
-        <v>3278.4</v>
+        <v>5013.8999999999996</v>
       </c>
       <c r="Q180" s="8">
         <v>0</v>
       </c>
       <c r="R180" s="8">
-        <v>3217.93</v>
+        <v>4100.2700000000004</v>
       </c>
       <c r="V180" s="7"/>
     </row>
     <row r="181" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>440</v>
+      </c>
+      <c r="B181" s="7">
+        <v>46300.631435185183</v>
+      </c>
+      <c r="C181" t="s">
+        <v>441</v>
+      </c>
+      <c r="D181" t="s">
+        <v>26</v>
+      </c>
+      <c r="E181" t="s">
+        <v>172</v>
+      </c>
+      <c r="F181" t="s">
         <v>442</v>
-      </c>
-      <c r="B181" s="7">
-        <v>46300.473171296297</v>
-      </c>
-      <c r="C181" t="s">
-        <v>443</v>
-      </c>
-      <c r="D181" t="s">
-        <v>260</v>
-      </c>
-      <c r="E181" t="s">
-        <v>444</v>
-      </c>
-      <c r="F181" t="s">
-        <v>446</v>
       </c>
       <c r="G181" t="s">
         <v>33</v>
       </c>
       <c r="H181" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I181" s="8">
-        <v>224.18</v>
+        <v>157.75</v>
       </c>
       <c r="J181" s="8">
-        <v>3362.7</v>
+        <v>3155</v>
       </c>
       <c r="K181" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L181" s="8">
-        <v>196.21</v>
+        <v>142.51</v>
       </c>
       <c r="M181" s="8">
-        <v>3924.2</v>
+        <v>4275.3</v>
       </c>
       <c r="N181" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O181" s="8">
-        <v>167.13</v>
+        <v>131.03</v>
       </c>
       <c r="P181" s="8">
-        <v>5013.8999999999996</v>
+        <v>5241.2</v>
       </c>
       <c r="Q181" s="8">
         <v>0</v>
       </c>
       <c r="R181" s="8">
-        <v>4100.2700000000004</v>
+        <v>4223.83</v>
       </c>
       <c r="V181" s="7"/>
     </row>
     <row r="182" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B182" s="7">
-        <v>46300.386967592596</v>
+        <v>46300.4137962963</v>
       </c>
       <c r="C182" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="D182" t="s">
         <v>26</v>
       </c>
       <c r="E182" t="s">
-        <v>449</v>
+        <v>119</v>
       </c>
       <c r="F182" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="G182" t="s">
-        <v>33</v>
+        <v>434</v>
       </c>
       <c r="H182" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I182" s="8">
-        <v>157.75</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="J182" s="8">
-        <v>3155</v>
+        <v>6610</v>
       </c>
       <c r="K182" s="1">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="L182" s="8">
-        <v>142.51</v>
+        <v>57.01</v>
       </c>
       <c r="M182" s="8">
-        <v>4275.3</v>
+        <v>8551.5</v>
       </c>
       <c r="N182" s="1">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="O182" s="8">
-        <v>131.03</v>
+        <v>51.7</v>
       </c>
       <c r="P182" s="8">
-        <v>5241.2</v>
+        <v>10340</v>
       </c>
       <c r="Q182" s="8">
         <v>0</v>
       </c>
       <c r="R182" s="8">
-        <v>4223.83</v>
+        <v>8500.5</v>
       </c>
       <c r="V182" s="7"/>
     </row>
     <row r="183" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="B183" s="7">
-        <v>46300.4137962963</v>
+        <v>46300.472534722219</v>
       </c>
       <c r="C183" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D183" t="s">
-        <v>26</v>
+        <v>260</v>
       </c>
       <c r="E183" t="s">
-        <v>119</v>
+        <v>437</v>
       </c>
       <c r="F183" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G183" t="s">
-        <v>441</v>
+        <v>33</v>
       </c>
       <c r="H183" s="1">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I183" s="8">
-        <v>66.099999999999994</v>
+        <v>26.78</v>
       </c>
       <c r="J183" s="8">
-        <v>6610</v>
+        <v>2811.9</v>
       </c>
       <c r="K183" s="1">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="L183" s="8">
-        <v>57.01</v>
+        <v>23.41</v>
       </c>
       <c r="M183" s="8">
-        <v>8551.5</v>
+        <v>3277.4</v>
       </c>
       <c r="N183" s="1">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="O183" s="8">
-        <v>51.7</v>
+        <v>20.58</v>
       </c>
       <c r="P183" s="8">
-        <v>10340</v>
+        <v>3910.2</v>
       </c>
       <c r="Q183" s="8">
         <v>0</v>
       </c>
       <c r="R183" s="8">
-        <v>8500.5</v>
+        <v>3333.17</v>
       </c>
       <c r="V183" s="7"/>
     </row>
     <row r="184" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B184" s="7">
-        <v>46300.472534722219</v>
+        <v>46300.55263888889</v>
       </c>
       <c r="C184" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D184" t="s">
-        <v>260</v>
+        <v>447</v>
       </c>
       <c r="E184" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F184" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G184" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H184" s="1">
-        <v>105</v>
+        <v>500</v>
       </c>
       <c r="I184" s="8">
-        <v>26.78</v>
+        <v>33.21</v>
       </c>
       <c r="J184" s="8">
-        <v>2811.9</v>
+        <v>16605</v>
       </c>
       <c r="K184" s="1">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="L184" s="8">
-        <v>23.41</v>
+        <v>26.37</v>
       </c>
       <c r="M184" s="8">
-        <v>3277.4</v>
+        <v>26370</v>
       </c>
       <c r="N184" s="1">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="O184" s="8">
-        <v>20.58</v>
+        <v>0</v>
       </c>
       <c r="P184" s="8">
-        <v>3910.2</v>
+        <v>0</v>
       </c>
       <c r="Q184" s="8">
         <v>0</v>
       </c>
       <c r="R184" s="8">
-        <v>3333.17</v>
+        <v>21487.5</v>
       </c>
       <c r="V184" s="7"/>
     </row>
@@ -12872,19 +12860,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{EF5C7CF5-8C00-456C-8DD8-5ABF8D289361}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U94 U99:U102 U113:U115" xr:uid="{121EC3EF-B2A5-479E-B3EB-F3B40103F2DC}">
       <formula1>"Preço, Prazo de entrega, Condição de Pagamento, Quantidade, Sem Retorno, Optou por outro produto"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{DF4BDE76-4E03-42FA-9D27-A355FF8DF3F9}">
+    <dataValidation type="list" allowBlank="1" sqref="S3:S94" xr:uid="{21B09B76-862B-4F3C-B625-E2BDA36E71AA}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{3D64CA54-2F7A-41F3-8D0F-B4B869F30452}">
+    <dataValidation type="list" allowBlank="1" sqref="D3:D1048576" xr:uid="{6F5E7BE0-E854-4FC8-B91E-1B73C8A18CA2}">
       <formula1>"AC,AL,AP,AM,BA,CE,DF,ES,GO,MA,MT,MS,MG,PA,PB,PR,PE,PI,RJ,RN,RS,RO,RR,SC,SP,SE,TO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{20E7D180-E016-4003-8150-66FA3A201DC3}">
+    <dataValidation type="list" allowBlank="1" sqref="T3:T1048576" xr:uid="{8E6456C2-B685-44AE-B0B7-E0726E83996B}">
       <formula1>"Mínima,2ª Opção,3ª Opção,-"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{3E729798-59A8-4ECF-9EB5-CF706C90FF98}">
+    <dataValidation type="list" allowBlank="1" sqref="S95:S1048576" xr:uid="{EABB983A-4CD2-4EE3-A9BC-83BC0C2C1C68}">
       <formula1>"Aprovado,Em Negociação,Perdido,Cancelado,Rascunho"</formula1>
     </dataValidation>
   </dataValidations>
